--- a/fims_arrival_rpa/입국신고_업무파일.xlsx
+++ b/fims_arrival_rpa/입국신고_업무파일.xlsx
@@ -751,10 +751,10 @@
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -767,7 +767,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>5행부터 입력하세요. 처리대상은 Y 또는 빈칸이면 포함되고 N이면 제외됩니다. 생년월일은 YYYYMMDD, 학번은 숫자 문자열로 입력하며 두 열 모두 텍스트 형식입니다. 현지추천단체·현지추천단체구분·최종출신학교는 비워두면 FIMS에 입력된 값을 그대로 둡니다. 값을 적으면(예: -) 그 값으로 덮어씁니다.</t>
+          <t>5행부터 입력하세요. 처리대상은 Y 또는 빈칸이면 포함되고 N이면 제외됩니다. 생년월일은 YYYYMMDD, 학번은 숫자 문자열로 입력하며 두 열 모두 텍스트 형식입니다. 현지추천단체구분·현지추천단체·최종출신학교는 비워두면 FIMS에 입력된 값을 그대로 둡니다. 값을 적으면(예: -) 그 값으로 덮어씁니다. 현지추천단체구분은 목록에서 고르세요.</t>
         </is>
       </c>
     </row>
@@ -794,22 +794,22 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
+          <t>현지추천단체구분</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>현지추천단체</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>최종출신학교</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
           <t>비고</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>현지추천단체</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>현지추천단체구분</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>최종출신학교</t>
         </is>
       </c>
     </row>
@@ -819,10 +819,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n"/>
+      <c r="B5" s="64" t="n"/>
       <c r="C5" s="64" t="n"/>
       <c r="D5" s="64" t="n"/>
-      <c r="E5" s="18" t="n"/>
+      <c r="E5" s="64" t="n"/>
       <c r="F5" s="64" t="n"/>
       <c r="G5" s="64" t="n"/>
       <c r="H5" s="64" t="n"/>
@@ -833,10 +833,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n"/>
-      <c r="C6" s="65" t="n"/>
-      <c r="D6" s="65" t="n"/>
-      <c r="E6" s="19" t="n"/>
+      <c r="B6" s="64" t="n"/>
+      <c r="C6" s="64" t="n"/>
+      <c r="D6" s="64" t="n"/>
+      <c r="E6" s="64" t="n"/>
       <c r="F6" s="64" t="n"/>
       <c r="G6" s="64" t="n"/>
       <c r="H6" s="64" t="n"/>
@@ -847,10 +847,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="65" t="n"/>
-      <c r="D7" s="65" t="n"/>
-      <c r="E7" s="19" t="n"/>
+      <c r="B7" s="64" t="n"/>
+      <c r="C7" s="64" t="n"/>
+      <c r="D7" s="64" t="n"/>
+      <c r="E7" s="64" t="n"/>
       <c r="F7" s="64" t="n"/>
       <c r="G7" s="64" t="n"/>
       <c r="H7" s="64" t="n"/>
@@ -861,10 +861,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="65" t="n"/>
-      <c r="D8" s="65" t="n"/>
-      <c r="E8" s="19" t="n"/>
+      <c r="B8" s="64" t="n"/>
+      <c r="C8" s="64" t="n"/>
+      <c r="D8" s="64" t="n"/>
+      <c r="E8" s="64" t="n"/>
       <c r="F8" s="64" t="n"/>
       <c r="G8" s="64" t="n"/>
       <c r="H8" s="64" t="n"/>
@@ -875,10 +875,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="65" t="n"/>
-      <c r="D9" s="65" t="n"/>
-      <c r="E9" s="19" t="n"/>
+      <c r="B9" s="64" t="n"/>
+      <c r="C9" s="64" t="n"/>
+      <c r="D9" s="64" t="n"/>
+      <c r="E9" s="64" t="n"/>
       <c r="F9" s="64" t="n"/>
       <c r="G9" s="64" t="n"/>
       <c r="H9" s="64" t="n"/>
@@ -889,10 +889,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n"/>
-      <c r="C10" s="65" t="n"/>
-      <c r="D10" s="65" t="n"/>
-      <c r="E10" s="19" t="n"/>
+      <c r="B10" s="64" t="n"/>
+      <c r="C10" s="64" t="n"/>
+      <c r="D10" s="64" t="n"/>
+      <c r="E10" s="64" t="n"/>
       <c r="F10" s="64" t="n"/>
       <c r="G10" s="64" t="n"/>
       <c r="H10" s="64" t="n"/>
@@ -903,10 +903,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="65" t="n"/>
-      <c r="D11" s="65" t="n"/>
-      <c r="E11" s="19" t="n"/>
+      <c r="B11" s="64" t="n"/>
+      <c r="C11" s="64" t="n"/>
+      <c r="D11" s="64" t="n"/>
+      <c r="E11" s="64" t="n"/>
       <c r="F11" s="64" t="n"/>
       <c r="G11" s="64" t="n"/>
       <c r="H11" s="64" t="n"/>
@@ -917,10 +917,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="65" t="n"/>
-      <c r="D12" s="65" t="n"/>
-      <c r="E12" s="19" t="n"/>
+      <c r="B12" s="64" t="n"/>
+      <c r="C12" s="64" t="n"/>
+      <c r="D12" s="64" t="n"/>
+      <c r="E12" s="64" t="n"/>
       <c r="F12" s="64" t="n"/>
       <c r="G12" s="64" t="n"/>
       <c r="H12" s="64" t="n"/>
@@ -931,10 +931,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="65" t="n"/>
-      <c r="D13" s="65" t="n"/>
-      <c r="E13" s="19" t="n"/>
+      <c r="B13" s="64" t="n"/>
+      <c r="C13" s="64" t="n"/>
+      <c r="D13" s="64" t="n"/>
+      <c r="E13" s="64" t="n"/>
       <c r="F13" s="64" t="n"/>
       <c r="G13" s="64" t="n"/>
       <c r="H13" s="64" t="n"/>
@@ -945,10 +945,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="65" t="n"/>
-      <c r="D14" s="65" t="n"/>
-      <c r="E14" s="19" t="n"/>
+      <c r="B14" s="64" t="n"/>
+      <c r="C14" s="64" t="n"/>
+      <c r="D14" s="64" t="n"/>
+      <c r="E14" s="64" t="n"/>
       <c r="F14" s="64" t="n"/>
       <c r="G14" s="64" t="n"/>
       <c r="H14" s="64" t="n"/>
@@ -959,10 +959,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="65" t="n"/>
-      <c r="D15" s="65" t="n"/>
-      <c r="E15" s="19" t="n"/>
+      <c r="B15" s="64" t="n"/>
+      <c r="C15" s="64" t="n"/>
+      <c r="D15" s="64" t="n"/>
+      <c r="E15" s="64" t="n"/>
       <c r="F15" s="64" t="n"/>
       <c r="G15" s="64" t="n"/>
       <c r="H15" s="64" t="n"/>
@@ -973,10 +973,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n"/>
-      <c r="C16" s="65" t="n"/>
-      <c r="D16" s="65" t="n"/>
-      <c r="E16" s="19" t="n"/>
+      <c r="B16" s="64" t="n"/>
+      <c r="C16" s="64" t="n"/>
+      <c r="D16" s="64" t="n"/>
+      <c r="E16" s="64" t="n"/>
       <c r="F16" s="64" t="n"/>
       <c r="G16" s="64" t="n"/>
       <c r="H16" s="64" t="n"/>
@@ -987,10 +987,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n"/>
-      <c r="C17" s="65" t="n"/>
-      <c r="D17" s="65" t="n"/>
-      <c r="E17" s="19" t="n"/>
+      <c r="B17" s="64" t="n"/>
+      <c r="C17" s="64" t="n"/>
+      <c r="D17" s="64" t="n"/>
+      <c r="E17" s="64" t="n"/>
       <c r="F17" s="64" t="n"/>
       <c r="G17" s="64" t="n"/>
       <c r="H17" s="64" t="n"/>
@@ -1001,10 +1001,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="65" t="n"/>
-      <c r="D18" s="65" t="n"/>
-      <c r="E18" s="19" t="n"/>
+      <c r="B18" s="64" t="n"/>
+      <c r="C18" s="64" t="n"/>
+      <c r="D18" s="64" t="n"/>
+      <c r="E18" s="64" t="n"/>
       <c r="F18" s="64" t="n"/>
       <c r="G18" s="64" t="n"/>
       <c r="H18" s="64" t="n"/>
@@ -1015,10 +1015,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="65" t="n"/>
-      <c r="D19" s="65" t="n"/>
-      <c r="E19" s="19" t="n"/>
+      <c r="B19" s="64" t="n"/>
+      <c r="C19" s="64" t="n"/>
+      <c r="D19" s="64" t="n"/>
+      <c r="E19" s="64" t="n"/>
       <c r="F19" s="64" t="n"/>
       <c r="G19" s="64" t="n"/>
       <c r="H19" s="64" t="n"/>
@@ -1029,10 +1029,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="65" t="n"/>
-      <c r="D20" s="65" t="n"/>
-      <c r="E20" s="19" t="n"/>
+      <c r="B20" s="64" t="n"/>
+      <c r="C20" s="64" t="n"/>
+      <c r="D20" s="64" t="n"/>
+      <c r="E20" s="64" t="n"/>
       <c r="F20" s="64" t="n"/>
       <c r="G20" s="64" t="n"/>
       <c r="H20" s="64" t="n"/>
@@ -1043,10 +1043,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="65" t="n"/>
-      <c r="D21" s="65" t="n"/>
-      <c r="E21" s="19" t="n"/>
+      <c r="B21" s="64" t="n"/>
+      <c r="C21" s="64" t="n"/>
+      <c r="D21" s="64" t="n"/>
+      <c r="E21" s="64" t="n"/>
       <c r="F21" s="64" t="n"/>
       <c r="G21" s="64" t="n"/>
       <c r="H21" s="64" t="n"/>
@@ -1057,10 +1057,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="65" t="n"/>
-      <c r="D22" s="65" t="n"/>
-      <c r="E22" s="19" t="n"/>
+      <c r="B22" s="64" t="n"/>
+      <c r="C22" s="64" t="n"/>
+      <c r="D22" s="64" t="n"/>
+      <c r="E22" s="64" t="n"/>
       <c r="F22" s="64" t="n"/>
       <c r="G22" s="64" t="n"/>
       <c r="H22" s="64" t="n"/>
@@ -1071,10 +1071,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="65" t="n"/>
-      <c r="D23" s="65" t="n"/>
-      <c r="E23" s="19" t="n"/>
+      <c r="B23" s="64" t="n"/>
+      <c r="C23" s="64" t="n"/>
+      <c r="D23" s="64" t="n"/>
+      <c r="E23" s="64" t="n"/>
       <c r="F23" s="64" t="n"/>
       <c r="G23" s="64" t="n"/>
       <c r="H23" s="64" t="n"/>
@@ -1085,10 +1085,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="65" t="n"/>
-      <c r="D24" s="65" t="n"/>
-      <c r="E24" s="19" t="n"/>
+      <c r="B24" s="64" t="n"/>
+      <c r="C24" s="64" t="n"/>
+      <c r="D24" s="64" t="n"/>
+      <c r="E24" s="64" t="n"/>
       <c r="F24" s="64" t="n"/>
       <c r="G24" s="64" t="n"/>
       <c r="H24" s="64" t="n"/>
@@ -1099,10 +1099,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="65" t="n"/>
-      <c r="D25" s="65" t="n"/>
-      <c r="E25" s="19" t="n"/>
+      <c r="B25" s="64" t="n"/>
+      <c r="C25" s="64" t="n"/>
+      <c r="D25" s="64" t="n"/>
+      <c r="E25" s="64" t="n"/>
       <c r="F25" s="64" t="n"/>
       <c r="G25" s="64" t="n"/>
       <c r="H25" s="64" t="n"/>
@@ -1113,10 +1113,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="65" t="n"/>
-      <c r="D26" s="65" t="n"/>
-      <c r="E26" s="19" t="n"/>
+      <c r="B26" s="64" t="n"/>
+      <c r="C26" s="64" t="n"/>
+      <c r="D26" s="64" t="n"/>
+      <c r="E26" s="64" t="n"/>
       <c r="F26" s="64" t="n"/>
       <c r="G26" s="64" t="n"/>
       <c r="H26" s="64" t="n"/>
@@ -1127,10 +1127,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="65" t="n"/>
-      <c r="D27" s="65" t="n"/>
-      <c r="E27" s="19" t="n"/>
+      <c r="B27" s="64" t="n"/>
+      <c r="C27" s="64" t="n"/>
+      <c r="D27" s="64" t="n"/>
+      <c r="E27" s="64" t="n"/>
       <c r="F27" s="64" t="n"/>
       <c r="G27" s="64" t="n"/>
       <c r="H27" s="64" t="n"/>
@@ -1141,10 +1141,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="65" t="n"/>
-      <c r="D28" s="65" t="n"/>
-      <c r="E28" s="19" t="n"/>
+      <c r="B28" s="64" t="n"/>
+      <c r="C28" s="64" t="n"/>
+      <c r="D28" s="64" t="n"/>
+      <c r="E28" s="64" t="n"/>
       <c r="F28" s="64" t="n"/>
       <c r="G28" s="64" t="n"/>
       <c r="H28" s="64" t="n"/>
@@ -1155,10 +1155,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="65" t="n"/>
-      <c r="D29" s="65" t="n"/>
-      <c r="E29" s="19" t="n"/>
+      <c r="B29" s="64" t="n"/>
+      <c r="C29" s="64" t="n"/>
+      <c r="D29" s="64" t="n"/>
+      <c r="E29" s="64" t="n"/>
       <c r="F29" s="64" t="n"/>
       <c r="G29" s="64" t="n"/>
       <c r="H29" s="64" t="n"/>
@@ -1169,10 +1169,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="65" t="n"/>
-      <c r="D30" s="65" t="n"/>
-      <c r="E30" s="19" t="n"/>
+      <c r="B30" s="64" t="n"/>
+      <c r="C30" s="64" t="n"/>
+      <c r="D30" s="64" t="n"/>
+      <c r="E30" s="64" t="n"/>
       <c r="F30" s="64" t="n"/>
       <c r="G30" s="64" t="n"/>
       <c r="H30" s="64" t="n"/>
@@ -1183,10 +1183,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="65" t="n"/>
-      <c r="D31" s="65" t="n"/>
-      <c r="E31" s="19" t="n"/>
+      <c r="B31" s="64" t="n"/>
+      <c r="C31" s="64" t="n"/>
+      <c r="D31" s="64" t="n"/>
+      <c r="E31" s="64" t="n"/>
       <c r="F31" s="64" t="n"/>
       <c r="G31" s="64" t="n"/>
       <c r="H31" s="64" t="n"/>
@@ -1197,10 +1197,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="65" t="n"/>
-      <c r="D32" s="65" t="n"/>
-      <c r="E32" s="19" t="n"/>
+      <c r="B32" s="64" t="n"/>
+      <c r="C32" s="64" t="n"/>
+      <c r="D32" s="64" t="n"/>
+      <c r="E32" s="64" t="n"/>
       <c r="F32" s="64" t="n"/>
       <c r="G32" s="64" t="n"/>
       <c r="H32" s="64" t="n"/>
@@ -1211,10 +1211,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="65" t="n"/>
-      <c r="D33" s="65" t="n"/>
-      <c r="E33" s="19" t="n"/>
+      <c r="B33" s="64" t="n"/>
+      <c r="C33" s="64" t="n"/>
+      <c r="D33" s="64" t="n"/>
+      <c r="E33" s="64" t="n"/>
       <c r="F33" s="64" t="n"/>
       <c r="G33" s="64" t="n"/>
       <c r="H33" s="64" t="n"/>
@@ -1225,10 +1225,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="65" t="n"/>
-      <c r="D34" s="65" t="n"/>
-      <c r="E34" s="19" t="n"/>
+      <c r="B34" s="64" t="n"/>
+      <c r="C34" s="64" t="n"/>
+      <c r="D34" s="64" t="n"/>
+      <c r="E34" s="64" t="n"/>
       <c r="F34" s="64" t="n"/>
       <c r="G34" s="64" t="n"/>
       <c r="H34" s="64" t="n"/>
@@ -1239,10 +1239,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="65" t="n"/>
-      <c r="D35" s="65" t="n"/>
-      <c r="E35" s="19" t="n"/>
+      <c r="B35" s="64" t="n"/>
+      <c r="C35" s="64" t="n"/>
+      <c r="D35" s="64" t="n"/>
+      <c r="E35" s="64" t="n"/>
       <c r="F35" s="64" t="n"/>
       <c r="G35" s="64" t="n"/>
       <c r="H35" s="64" t="n"/>
@@ -1253,10 +1253,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="65" t="n"/>
-      <c r="D36" s="65" t="n"/>
-      <c r="E36" s="19" t="n"/>
+      <c r="B36" s="64" t="n"/>
+      <c r="C36" s="64" t="n"/>
+      <c r="D36" s="64" t="n"/>
+      <c r="E36" s="64" t="n"/>
       <c r="F36" s="64" t="n"/>
       <c r="G36" s="64" t="n"/>
       <c r="H36" s="64" t="n"/>
@@ -1267,10 +1267,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="65" t="n"/>
-      <c r="D37" s="65" t="n"/>
-      <c r="E37" s="19" t="n"/>
+      <c r="B37" s="64" t="n"/>
+      <c r="C37" s="64" t="n"/>
+      <c r="D37" s="64" t="n"/>
+      <c r="E37" s="64" t="n"/>
       <c r="F37" s="64" t="n"/>
       <c r="G37" s="64" t="n"/>
       <c r="H37" s="64" t="n"/>
@@ -1281,10 +1281,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="65" t="n"/>
-      <c r="D38" s="65" t="n"/>
-      <c r="E38" s="19" t="n"/>
+      <c r="B38" s="64" t="n"/>
+      <c r="C38" s="64" t="n"/>
+      <c r="D38" s="64" t="n"/>
+      <c r="E38" s="64" t="n"/>
       <c r="F38" s="64" t="n"/>
       <c r="G38" s="64" t="n"/>
       <c r="H38" s="64" t="n"/>
@@ -1295,10 +1295,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="65" t="n"/>
-      <c r="D39" s="65" t="n"/>
-      <c r="E39" s="19" t="n"/>
+      <c r="B39" s="64" t="n"/>
+      <c r="C39" s="64" t="n"/>
+      <c r="D39" s="64" t="n"/>
+      <c r="E39" s="64" t="n"/>
       <c r="F39" s="64" t="n"/>
       <c r="G39" s="64" t="n"/>
       <c r="H39" s="64" t="n"/>
@@ -1309,10 +1309,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="65" t="n"/>
-      <c r="D40" s="65" t="n"/>
-      <c r="E40" s="19" t="n"/>
+      <c r="B40" s="64" t="n"/>
+      <c r="C40" s="64" t="n"/>
+      <c r="D40" s="64" t="n"/>
+      <c r="E40" s="64" t="n"/>
       <c r="F40" s="64" t="n"/>
       <c r="G40" s="64" t="n"/>
       <c r="H40" s="64" t="n"/>
@@ -1323,10 +1323,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="65" t="n"/>
-      <c r="D41" s="65" t="n"/>
-      <c r="E41" s="19" t="n"/>
+      <c r="B41" s="64" t="n"/>
+      <c r="C41" s="64" t="n"/>
+      <c r="D41" s="64" t="n"/>
+      <c r="E41" s="64" t="n"/>
       <c r="F41" s="64" t="n"/>
       <c r="G41" s="64" t="n"/>
       <c r="H41" s="64" t="n"/>
@@ -1337,10 +1337,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B42" s="19" t="n"/>
-      <c r="C42" s="65" t="n"/>
-      <c r="D42" s="65" t="n"/>
-      <c r="E42" s="19" t="n"/>
+      <c r="B42" s="64" t="n"/>
+      <c r="C42" s="64" t="n"/>
+      <c r="D42" s="64" t="n"/>
+      <c r="E42" s="64" t="n"/>
       <c r="F42" s="64" t="n"/>
       <c r="G42" s="64" t="n"/>
       <c r="H42" s="64" t="n"/>
@@ -1351,10 +1351,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="65" t="n"/>
-      <c r="D43" s="65" t="n"/>
-      <c r="E43" s="19" t="n"/>
+      <c r="B43" s="64" t="n"/>
+      <c r="C43" s="64" t="n"/>
+      <c r="D43" s="64" t="n"/>
+      <c r="E43" s="64" t="n"/>
       <c r="F43" s="64" t="n"/>
       <c r="G43" s="64" t="n"/>
       <c r="H43" s="64" t="n"/>
@@ -1365,10 +1365,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B44" s="19" t="n"/>
-      <c r="C44" s="65" t="n"/>
-      <c r="D44" s="65" t="n"/>
-      <c r="E44" s="19" t="n"/>
+      <c r="B44" s="64" t="n"/>
+      <c r="C44" s="64" t="n"/>
+      <c r="D44" s="64" t="n"/>
+      <c r="E44" s="64" t="n"/>
       <c r="F44" s="64" t="n"/>
       <c r="G44" s="64" t="n"/>
       <c r="H44" s="64" t="n"/>
@@ -1379,10 +1379,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="65" t="n"/>
-      <c r="D45" s="65" t="n"/>
-      <c r="E45" s="19" t="n"/>
+      <c r="B45" s="64" t="n"/>
+      <c r="C45" s="64" t="n"/>
+      <c r="D45" s="64" t="n"/>
+      <c r="E45" s="64" t="n"/>
       <c r="F45" s="64" t="n"/>
       <c r="G45" s="64" t="n"/>
       <c r="H45" s="64" t="n"/>
@@ -1393,10 +1393,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="65" t="n"/>
-      <c r="D46" s="65" t="n"/>
-      <c r="E46" s="19" t="n"/>
+      <c r="B46" s="64" t="n"/>
+      <c r="C46" s="64" t="n"/>
+      <c r="D46" s="64" t="n"/>
+      <c r="E46" s="64" t="n"/>
       <c r="F46" s="64" t="n"/>
       <c r="G46" s="64" t="n"/>
       <c r="H46" s="64" t="n"/>
@@ -1407,10 +1407,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B47" s="19" t="n"/>
-      <c r="C47" s="65" t="n"/>
-      <c r="D47" s="65" t="n"/>
-      <c r="E47" s="19" t="n"/>
+      <c r="B47" s="64" t="n"/>
+      <c r="C47" s="64" t="n"/>
+      <c r="D47" s="64" t="n"/>
+      <c r="E47" s="64" t="n"/>
       <c r="F47" s="64" t="n"/>
       <c r="G47" s="64" t="n"/>
       <c r="H47" s="64" t="n"/>
@@ -1421,10 +1421,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="65" t="n"/>
-      <c r="D48" s="65" t="n"/>
-      <c r="E48" s="19" t="n"/>
+      <c r="B48" s="64" t="n"/>
+      <c r="C48" s="64" t="n"/>
+      <c r="D48" s="64" t="n"/>
+      <c r="E48" s="64" t="n"/>
       <c r="F48" s="64" t="n"/>
       <c r="G48" s="64" t="n"/>
       <c r="H48" s="64" t="n"/>
@@ -1435,10 +1435,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B49" s="19" t="n"/>
-      <c r="C49" s="65" t="n"/>
-      <c r="D49" s="65" t="n"/>
-      <c r="E49" s="19" t="n"/>
+      <c r="B49" s="64" t="n"/>
+      <c r="C49" s="64" t="n"/>
+      <c r="D49" s="64" t="n"/>
+      <c r="E49" s="64" t="n"/>
       <c r="F49" s="64" t="n"/>
       <c r="G49" s="64" t="n"/>
       <c r="H49" s="64" t="n"/>
@@ -1449,10 +1449,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="65" t="n"/>
-      <c r="D50" s="65" t="n"/>
-      <c r="E50" s="19" t="n"/>
+      <c r="B50" s="64" t="n"/>
+      <c r="C50" s="64" t="n"/>
+      <c r="D50" s="64" t="n"/>
+      <c r="E50" s="64" t="n"/>
       <c r="F50" s="64" t="n"/>
       <c r="G50" s="64" t="n"/>
       <c r="H50" s="64" t="n"/>
@@ -1463,10 +1463,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="65" t="n"/>
-      <c r="D51" s="65" t="n"/>
-      <c r="E51" s="19" t="n"/>
+      <c r="B51" s="64" t="n"/>
+      <c r="C51" s="64" t="n"/>
+      <c r="D51" s="64" t="n"/>
+      <c r="E51" s="64" t="n"/>
       <c r="F51" s="64" t="n"/>
       <c r="G51" s="64" t="n"/>
       <c r="H51" s="64" t="n"/>
@@ -1477,10 +1477,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B52" s="19" t="n"/>
-      <c r="C52" s="65" t="n"/>
-      <c r="D52" s="65" t="n"/>
-      <c r="E52" s="19" t="n"/>
+      <c r="B52" s="64" t="n"/>
+      <c r="C52" s="64" t="n"/>
+      <c r="D52" s="64" t="n"/>
+      <c r="E52" s="64" t="n"/>
       <c r="F52" s="64" t="n"/>
       <c r="G52" s="64" t="n"/>
       <c r="H52" s="64" t="n"/>
@@ -1491,10 +1491,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="65" t="n"/>
-      <c r="D53" s="65" t="n"/>
-      <c r="E53" s="19" t="n"/>
+      <c r="B53" s="64" t="n"/>
+      <c r="C53" s="64" t="n"/>
+      <c r="D53" s="64" t="n"/>
+      <c r="E53" s="64" t="n"/>
       <c r="F53" s="64" t="n"/>
       <c r="G53" s="64" t="n"/>
       <c r="H53" s="64" t="n"/>
@@ -1505,10 +1505,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B54" s="19" t="n"/>
-      <c r="C54" s="65" t="n"/>
-      <c r="D54" s="65" t="n"/>
-      <c r="E54" s="19" t="n"/>
+      <c r="B54" s="64" t="n"/>
+      <c r="C54" s="64" t="n"/>
+      <c r="D54" s="64" t="n"/>
+      <c r="E54" s="64" t="n"/>
       <c r="F54" s="64" t="n"/>
       <c r="G54" s="64" t="n"/>
       <c r="H54" s="64" t="n"/>
@@ -1519,10 +1519,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B55" s="19" t="n"/>
-      <c r="C55" s="65" t="n"/>
-      <c r="D55" s="65" t="n"/>
-      <c r="E55" s="19" t="n"/>
+      <c r="B55" s="64" t="n"/>
+      <c r="C55" s="64" t="n"/>
+      <c r="D55" s="64" t="n"/>
+      <c r="E55" s="64" t="n"/>
       <c r="F55" s="64" t="n"/>
       <c r="G55" s="64" t="n"/>
       <c r="H55" s="64" t="n"/>
@@ -1533,10 +1533,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B56" s="19" t="n"/>
-      <c r="C56" s="65" t="n"/>
-      <c r="D56" s="65" t="n"/>
-      <c r="E56" s="19" t="n"/>
+      <c r="B56" s="64" t="n"/>
+      <c r="C56" s="64" t="n"/>
+      <c r="D56" s="64" t="n"/>
+      <c r="E56" s="64" t="n"/>
       <c r="F56" s="64" t="n"/>
       <c r="G56" s="64" t="n"/>
       <c r="H56" s="64" t="n"/>
@@ -1547,10 +1547,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="65" t="n"/>
-      <c r="D57" s="65" t="n"/>
-      <c r="E57" s="19" t="n"/>
+      <c r="B57" s="64" t="n"/>
+      <c r="C57" s="64" t="n"/>
+      <c r="D57" s="64" t="n"/>
+      <c r="E57" s="64" t="n"/>
       <c r="F57" s="64" t="n"/>
       <c r="G57" s="64" t="n"/>
       <c r="H57" s="64" t="n"/>
@@ -1561,10 +1561,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="65" t="n"/>
-      <c r="D58" s="65" t="n"/>
-      <c r="E58" s="19" t="n"/>
+      <c r="B58" s="64" t="n"/>
+      <c r="C58" s="64" t="n"/>
+      <c r="D58" s="64" t="n"/>
+      <c r="E58" s="64" t="n"/>
       <c r="F58" s="64" t="n"/>
       <c r="G58" s="64" t="n"/>
       <c r="H58" s="64" t="n"/>
@@ -1575,10 +1575,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B59" s="19" t="n"/>
-      <c r="C59" s="65" t="n"/>
-      <c r="D59" s="65" t="n"/>
-      <c r="E59" s="19" t="n"/>
+      <c r="B59" s="64" t="n"/>
+      <c r="C59" s="64" t="n"/>
+      <c r="D59" s="64" t="n"/>
+      <c r="E59" s="64" t="n"/>
       <c r="F59" s="64" t="n"/>
       <c r="G59" s="64" t="n"/>
       <c r="H59" s="64" t="n"/>
@@ -1589,10 +1589,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B60" s="19" t="n"/>
-      <c r="C60" s="65" t="n"/>
-      <c r="D60" s="65" t="n"/>
-      <c r="E60" s="19" t="n"/>
+      <c r="B60" s="64" t="n"/>
+      <c r="C60" s="64" t="n"/>
+      <c r="D60" s="64" t="n"/>
+      <c r="E60" s="64" t="n"/>
       <c r="F60" s="64" t="n"/>
       <c r="G60" s="64" t="n"/>
       <c r="H60" s="64" t="n"/>
@@ -1603,10 +1603,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="65" t="n"/>
-      <c r="D61" s="65" t="n"/>
-      <c r="E61" s="19" t="n"/>
+      <c r="B61" s="64" t="n"/>
+      <c r="C61" s="64" t="n"/>
+      <c r="D61" s="64" t="n"/>
+      <c r="E61" s="64" t="n"/>
       <c r="F61" s="64" t="n"/>
       <c r="G61" s="64" t="n"/>
       <c r="H61" s="64" t="n"/>
@@ -1617,10 +1617,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B62" s="19" t="n"/>
-      <c r="C62" s="65" t="n"/>
-      <c r="D62" s="65" t="n"/>
-      <c r="E62" s="19" t="n"/>
+      <c r="B62" s="64" t="n"/>
+      <c r="C62" s="64" t="n"/>
+      <c r="D62" s="64" t="n"/>
+      <c r="E62" s="64" t="n"/>
       <c r="F62" s="64" t="n"/>
       <c r="G62" s="64" t="n"/>
       <c r="H62" s="64" t="n"/>
@@ -1631,10 +1631,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B63" s="19" t="n"/>
-      <c r="C63" s="65" t="n"/>
-      <c r="D63" s="65" t="n"/>
-      <c r="E63" s="19" t="n"/>
+      <c r="B63" s="64" t="n"/>
+      <c r="C63" s="64" t="n"/>
+      <c r="D63" s="64" t="n"/>
+      <c r="E63" s="64" t="n"/>
       <c r="F63" s="64" t="n"/>
       <c r="G63" s="64" t="n"/>
       <c r="H63" s="64" t="n"/>
@@ -1645,10 +1645,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B64" s="19" t="n"/>
-      <c r="C64" s="65" t="n"/>
-      <c r="D64" s="65" t="n"/>
-      <c r="E64" s="19" t="n"/>
+      <c r="B64" s="64" t="n"/>
+      <c r="C64" s="64" t="n"/>
+      <c r="D64" s="64" t="n"/>
+      <c r="E64" s="64" t="n"/>
       <c r="F64" s="64" t="n"/>
       <c r="G64" s="64" t="n"/>
       <c r="H64" s="64" t="n"/>
@@ -1659,10 +1659,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B65" s="19" t="n"/>
-      <c r="C65" s="65" t="n"/>
-      <c r="D65" s="65" t="n"/>
-      <c r="E65" s="19" t="n"/>
+      <c r="B65" s="64" t="n"/>
+      <c r="C65" s="64" t="n"/>
+      <c r="D65" s="64" t="n"/>
+      <c r="E65" s="64" t="n"/>
       <c r="F65" s="64" t="n"/>
       <c r="G65" s="64" t="n"/>
       <c r="H65" s="64" t="n"/>
@@ -1673,10 +1673,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B66" s="19" t="n"/>
-      <c r="C66" s="65" t="n"/>
-      <c r="D66" s="65" t="n"/>
-      <c r="E66" s="19" t="n"/>
+      <c r="B66" s="64" t="n"/>
+      <c r="C66" s="64" t="n"/>
+      <c r="D66" s="64" t="n"/>
+      <c r="E66" s="64" t="n"/>
       <c r="F66" s="64" t="n"/>
       <c r="G66" s="64" t="n"/>
       <c r="H66" s="64" t="n"/>
@@ -1687,10 +1687,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B67" s="19" t="n"/>
-      <c r="C67" s="65" t="n"/>
-      <c r="D67" s="65" t="n"/>
-      <c r="E67" s="19" t="n"/>
+      <c r="B67" s="64" t="n"/>
+      <c r="C67" s="64" t="n"/>
+      <c r="D67" s="64" t="n"/>
+      <c r="E67" s="64" t="n"/>
       <c r="F67" s="64" t="n"/>
       <c r="G67" s="64" t="n"/>
       <c r="H67" s="64" t="n"/>
@@ -1701,10 +1701,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B68" s="19" t="n"/>
-      <c r="C68" s="65" t="n"/>
-      <c r="D68" s="65" t="n"/>
-      <c r="E68" s="19" t="n"/>
+      <c r="B68" s="64" t="n"/>
+      <c r="C68" s="64" t="n"/>
+      <c r="D68" s="64" t="n"/>
+      <c r="E68" s="64" t="n"/>
       <c r="F68" s="64" t="n"/>
       <c r="G68" s="64" t="n"/>
       <c r="H68" s="64" t="n"/>
@@ -1715,10 +1715,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B69" s="19" t="n"/>
-      <c r="C69" s="65" t="n"/>
-      <c r="D69" s="65" t="n"/>
-      <c r="E69" s="19" t="n"/>
+      <c r="B69" s="64" t="n"/>
+      <c r="C69" s="64" t="n"/>
+      <c r="D69" s="64" t="n"/>
+      <c r="E69" s="64" t="n"/>
       <c r="F69" s="64" t="n"/>
       <c r="G69" s="64" t="n"/>
       <c r="H69" s="64" t="n"/>
@@ -1729,10 +1729,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B70" s="19" t="n"/>
-      <c r="C70" s="65" t="n"/>
-      <c r="D70" s="65" t="n"/>
-      <c r="E70" s="19" t="n"/>
+      <c r="B70" s="64" t="n"/>
+      <c r="C70" s="64" t="n"/>
+      <c r="D70" s="64" t="n"/>
+      <c r="E70" s="64" t="n"/>
       <c r="F70" s="64" t="n"/>
       <c r="G70" s="64" t="n"/>
       <c r="H70" s="64" t="n"/>
@@ -1743,10 +1743,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B71" s="19" t="n"/>
-      <c r="C71" s="65" t="n"/>
-      <c r="D71" s="65" t="n"/>
-      <c r="E71" s="19" t="n"/>
+      <c r="B71" s="64" t="n"/>
+      <c r="C71" s="64" t="n"/>
+      <c r="D71" s="64" t="n"/>
+      <c r="E71" s="64" t="n"/>
       <c r="F71" s="64" t="n"/>
       <c r="G71" s="64" t="n"/>
       <c r="H71" s="64" t="n"/>
@@ -1757,10 +1757,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B72" s="19" t="n"/>
-      <c r="C72" s="65" t="n"/>
-      <c r="D72" s="65" t="n"/>
-      <c r="E72" s="19" t="n"/>
+      <c r="B72" s="64" t="n"/>
+      <c r="C72" s="64" t="n"/>
+      <c r="D72" s="64" t="n"/>
+      <c r="E72" s="64" t="n"/>
       <c r="F72" s="64" t="n"/>
       <c r="G72" s="64" t="n"/>
       <c r="H72" s="64" t="n"/>
@@ -1771,10 +1771,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B73" s="19" t="n"/>
-      <c r="C73" s="65" t="n"/>
-      <c r="D73" s="65" t="n"/>
-      <c r="E73" s="19" t="n"/>
+      <c r="B73" s="64" t="n"/>
+      <c r="C73" s="64" t="n"/>
+      <c r="D73" s="64" t="n"/>
+      <c r="E73" s="64" t="n"/>
       <c r="F73" s="64" t="n"/>
       <c r="G73" s="64" t="n"/>
       <c r="H73" s="64" t="n"/>
@@ -1785,10 +1785,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B74" s="19" t="n"/>
-      <c r="C74" s="65" t="n"/>
-      <c r="D74" s="65" t="n"/>
-      <c r="E74" s="19" t="n"/>
+      <c r="B74" s="64" t="n"/>
+      <c r="C74" s="64" t="n"/>
+      <c r="D74" s="64" t="n"/>
+      <c r="E74" s="64" t="n"/>
       <c r="F74" s="64" t="n"/>
       <c r="G74" s="64" t="n"/>
       <c r="H74" s="64" t="n"/>
@@ -1799,10 +1799,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B75" s="19" t="n"/>
-      <c r="C75" s="65" t="n"/>
-      <c r="D75" s="65" t="n"/>
-      <c r="E75" s="19" t="n"/>
+      <c r="B75" s="64" t="n"/>
+      <c r="C75" s="64" t="n"/>
+      <c r="D75" s="64" t="n"/>
+      <c r="E75" s="64" t="n"/>
       <c r="F75" s="64" t="n"/>
       <c r="G75" s="64" t="n"/>
       <c r="H75" s="64" t="n"/>
@@ -1813,10 +1813,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B76" s="19" t="n"/>
-      <c r="C76" s="65" t="n"/>
-      <c r="D76" s="65" t="n"/>
-      <c r="E76" s="19" t="n"/>
+      <c r="B76" s="64" t="n"/>
+      <c r="C76" s="64" t="n"/>
+      <c r="D76" s="64" t="n"/>
+      <c r="E76" s="64" t="n"/>
       <c r="F76" s="64" t="n"/>
       <c r="G76" s="64" t="n"/>
       <c r="H76" s="64" t="n"/>
@@ -1827,10 +1827,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B77" s="19" t="n"/>
-      <c r="C77" s="65" t="n"/>
-      <c r="D77" s="65" t="n"/>
-      <c r="E77" s="19" t="n"/>
+      <c r="B77" s="64" t="n"/>
+      <c r="C77" s="64" t="n"/>
+      <c r="D77" s="64" t="n"/>
+      <c r="E77" s="64" t="n"/>
       <c r="F77" s="64" t="n"/>
       <c r="G77" s="64" t="n"/>
       <c r="H77" s="64" t="n"/>
@@ -1841,10 +1841,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B78" s="19" t="n"/>
-      <c r="C78" s="65" t="n"/>
-      <c r="D78" s="65" t="n"/>
-      <c r="E78" s="19" t="n"/>
+      <c r="B78" s="64" t="n"/>
+      <c r="C78" s="64" t="n"/>
+      <c r="D78" s="64" t="n"/>
+      <c r="E78" s="64" t="n"/>
       <c r="F78" s="64" t="n"/>
       <c r="G78" s="64" t="n"/>
       <c r="H78" s="64" t="n"/>
@@ -1855,10 +1855,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B79" s="19" t="n"/>
-      <c r="C79" s="65" t="n"/>
-      <c r="D79" s="65" t="n"/>
-      <c r="E79" s="19" t="n"/>
+      <c r="B79" s="64" t="n"/>
+      <c r="C79" s="64" t="n"/>
+      <c r="D79" s="64" t="n"/>
+      <c r="E79" s="64" t="n"/>
       <c r="F79" s="64" t="n"/>
       <c r="G79" s="64" t="n"/>
       <c r="H79" s="64" t="n"/>
@@ -1869,10 +1869,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B80" s="19" t="n"/>
-      <c r="C80" s="65" t="n"/>
-      <c r="D80" s="65" t="n"/>
-      <c r="E80" s="19" t="n"/>
+      <c r="B80" s="64" t="n"/>
+      <c r="C80" s="64" t="n"/>
+      <c r="D80" s="64" t="n"/>
+      <c r="E80" s="64" t="n"/>
       <c r="F80" s="64" t="n"/>
       <c r="G80" s="64" t="n"/>
       <c r="H80" s="64" t="n"/>
@@ -1883,10 +1883,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B81" s="19" t="n"/>
-      <c r="C81" s="65" t="n"/>
-      <c r="D81" s="65" t="n"/>
-      <c r="E81" s="19" t="n"/>
+      <c r="B81" s="64" t="n"/>
+      <c r="C81" s="64" t="n"/>
+      <c r="D81" s="64" t="n"/>
+      <c r="E81" s="64" t="n"/>
       <c r="F81" s="64" t="n"/>
       <c r="G81" s="64" t="n"/>
       <c r="H81" s="64" t="n"/>
@@ -1897,10 +1897,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B82" s="19" t="n"/>
-      <c r="C82" s="65" t="n"/>
-      <c r="D82" s="65" t="n"/>
-      <c r="E82" s="19" t="n"/>
+      <c r="B82" s="64" t="n"/>
+      <c r="C82" s="64" t="n"/>
+      <c r="D82" s="64" t="n"/>
+      <c r="E82" s="64" t="n"/>
       <c r="F82" s="64" t="n"/>
       <c r="G82" s="64" t="n"/>
       <c r="H82" s="64" t="n"/>
@@ -1911,10 +1911,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B83" s="19" t="n"/>
-      <c r="C83" s="65" t="n"/>
-      <c r="D83" s="65" t="n"/>
-      <c r="E83" s="19" t="n"/>
+      <c r="B83" s="64" t="n"/>
+      <c r="C83" s="64" t="n"/>
+      <c r="D83" s="64" t="n"/>
+      <c r="E83" s="64" t="n"/>
       <c r="F83" s="64" t="n"/>
       <c r="G83" s="64" t="n"/>
       <c r="H83" s="64" t="n"/>
@@ -1925,10 +1925,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B84" s="19" t="n"/>
-      <c r="C84" s="65" t="n"/>
-      <c r="D84" s="65" t="n"/>
-      <c r="E84" s="19" t="n"/>
+      <c r="B84" s="64" t="n"/>
+      <c r="C84" s="64" t="n"/>
+      <c r="D84" s="64" t="n"/>
+      <c r="E84" s="64" t="n"/>
       <c r="F84" s="64" t="n"/>
       <c r="G84" s="64" t="n"/>
       <c r="H84" s="64" t="n"/>
@@ -1939,10 +1939,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B85" s="19" t="n"/>
-      <c r="C85" s="65" t="n"/>
-      <c r="D85" s="65" t="n"/>
-      <c r="E85" s="19" t="n"/>
+      <c r="B85" s="64" t="n"/>
+      <c r="C85" s="64" t="n"/>
+      <c r="D85" s="64" t="n"/>
+      <c r="E85" s="64" t="n"/>
       <c r="F85" s="64" t="n"/>
       <c r="G85" s="64" t="n"/>
       <c r="H85" s="64" t="n"/>
@@ -1953,10 +1953,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B86" s="19" t="n"/>
-      <c r="C86" s="65" t="n"/>
-      <c r="D86" s="65" t="n"/>
-      <c r="E86" s="19" t="n"/>
+      <c r="B86" s="64" t="n"/>
+      <c r="C86" s="64" t="n"/>
+      <c r="D86" s="64" t="n"/>
+      <c r="E86" s="64" t="n"/>
       <c r="F86" s="64" t="n"/>
       <c r="G86" s="64" t="n"/>
       <c r="H86" s="64" t="n"/>
@@ -1967,10 +1967,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B87" s="19" t="n"/>
-      <c r="C87" s="65" t="n"/>
-      <c r="D87" s="65" t="n"/>
-      <c r="E87" s="19" t="n"/>
+      <c r="B87" s="64" t="n"/>
+      <c r="C87" s="64" t="n"/>
+      <c r="D87" s="64" t="n"/>
+      <c r="E87" s="64" t="n"/>
       <c r="F87" s="64" t="n"/>
       <c r="G87" s="64" t="n"/>
       <c r="H87" s="64" t="n"/>
@@ -1981,10 +1981,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B88" s="19" t="n"/>
-      <c r="C88" s="65" t="n"/>
-      <c r="D88" s="65" t="n"/>
-      <c r="E88" s="19" t="n"/>
+      <c r="B88" s="64" t="n"/>
+      <c r="C88" s="64" t="n"/>
+      <c r="D88" s="64" t="n"/>
+      <c r="E88" s="64" t="n"/>
       <c r="F88" s="64" t="n"/>
       <c r="G88" s="64" t="n"/>
       <c r="H88" s="64" t="n"/>
@@ -1995,10 +1995,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B89" s="19" t="n"/>
-      <c r="C89" s="65" t="n"/>
-      <c r="D89" s="65" t="n"/>
-      <c r="E89" s="19" t="n"/>
+      <c r="B89" s="64" t="n"/>
+      <c r="C89" s="64" t="n"/>
+      <c r="D89" s="64" t="n"/>
+      <c r="E89" s="64" t="n"/>
       <c r="F89" s="64" t="n"/>
       <c r="G89" s="64" t="n"/>
       <c r="H89" s="64" t="n"/>
@@ -2009,10 +2009,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B90" s="19" t="n"/>
-      <c r="C90" s="65" t="n"/>
-      <c r="D90" s="65" t="n"/>
-      <c r="E90" s="19" t="n"/>
+      <c r="B90" s="64" t="n"/>
+      <c r="C90" s="64" t="n"/>
+      <c r="D90" s="64" t="n"/>
+      <c r="E90" s="64" t="n"/>
       <c r="F90" s="64" t="n"/>
       <c r="G90" s="64" t="n"/>
       <c r="H90" s="64" t="n"/>
@@ -2023,10 +2023,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B91" s="19" t="n"/>
-      <c r="C91" s="65" t="n"/>
-      <c r="D91" s="65" t="n"/>
-      <c r="E91" s="19" t="n"/>
+      <c r="B91" s="64" t="n"/>
+      <c r="C91" s="64" t="n"/>
+      <c r="D91" s="64" t="n"/>
+      <c r="E91" s="64" t="n"/>
       <c r="F91" s="64" t="n"/>
       <c r="G91" s="64" t="n"/>
       <c r="H91" s="64" t="n"/>
@@ -2037,10 +2037,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B92" s="19" t="n"/>
-      <c r="C92" s="65" t="n"/>
-      <c r="D92" s="65" t="n"/>
-      <c r="E92" s="19" t="n"/>
+      <c r="B92" s="64" t="n"/>
+      <c r="C92" s="64" t="n"/>
+      <c r="D92" s="64" t="n"/>
+      <c r="E92" s="64" t="n"/>
       <c r="F92" s="64" t="n"/>
       <c r="G92" s="64" t="n"/>
       <c r="H92" s="64" t="n"/>
@@ -2051,10 +2051,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B93" s="19" t="n"/>
-      <c r="C93" s="65" t="n"/>
-      <c r="D93" s="65" t="n"/>
-      <c r="E93" s="19" t="n"/>
+      <c r="B93" s="64" t="n"/>
+      <c r="C93" s="64" t="n"/>
+      <c r="D93" s="64" t="n"/>
+      <c r="E93" s="64" t="n"/>
       <c r="F93" s="64" t="n"/>
       <c r="G93" s="64" t="n"/>
       <c r="H93" s="64" t="n"/>
@@ -2065,10 +2065,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B94" s="19" t="n"/>
-      <c r="C94" s="65" t="n"/>
-      <c r="D94" s="65" t="n"/>
-      <c r="E94" s="19" t="n"/>
+      <c r="B94" s="64" t="n"/>
+      <c r="C94" s="64" t="n"/>
+      <c r="D94" s="64" t="n"/>
+      <c r="E94" s="64" t="n"/>
       <c r="F94" s="64" t="n"/>
       <c r="G94" s="64" t="n"/>
       <c r="H94" s="64" t="n"/>
@@ -2079,10 +2079,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B95" s="19" t="n"/>
-      <c r="C95" s="65" t="n"/>
-      <c r="D95" s="65" t="n"/>
-      <c r="E95" s="19" t="n"/>
+      <c r="B95" s="64" t="n"/>
+      <c r="C95" s="64" t="n"/>
+      <c r="D95" s="64" t="n"/>
+      <c r="E95" s="64" t="n"/>
       <c r="F95" s="64" t="n"/>
       <c r="G95" s="64" t="n"/>
       <c r="H95" s="64" t="n"/>
@@ -2093,10 +2093,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B96" s="19" t="n"/>
-      <c r="C96" s="65" t="n"/>
-      <c r="D96" s="65" t="n"/>
-      <c r="E96" s="19" t="n"/>
+      <c r="B96" s="64" t="n"/>
+      <c r="C96" s="64" t="n"/>
+      <c r="D96" s="64" t="n"/>
+      <c r="E96" s="64" t="n"/>
       <c r="F96" s="64" t="n"/>
       <c r="G96" s="64" t="n"/>
       <c r="H96" s="64" t="n"/>
@@ -2107,10 +2107,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B97" s="19" t="n"/>
-      <c r="C97" s="65" t="n"/>
-      <c r="D97" s="65" t="n"/>
-      <c r="E97" s="19" t="n"/>
+      <c r="B97" s="64" t="n"/>
+      <c r="C97" s="64" t="n"/>
+      <c r="D97" s="64" t="n"/>
+      <c r="E97" s="64" t="n"/>
       <c r="F97" s="64" t="n"/>
       <c r="G97" s="64" t="n"/>
       <c r="H97" s="64" t="n"/>
@@ -2121,10 +2121,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B98" s="19" t="n"/>
-      <c r="C98" s="65" t="n"/>
-      <c r="D98" s="65" t="n"/>
-      <c r="E98" s="19" t="n"/>
+      <c r="B98" s="64" t="n"/>
+      <c r="C98" s="64" t="n"/>
+      <c r="D98" s="64" t="n"/>
+      <c r="E98" s="64" t="n"/>
       <c r="F98" s="64" t="n"/>
       <c r="G98" s="64" t="n"/>
       <c r="H98" s="64" t="n"/>
@@ -2135,10 +2135,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B99" s="19" t="n"/>
-      <c r="C99" s="65" t="n"/>
-      <c r="D99" s="65" t="n"/>
-      <c r="E99" s="19" t="n"/>
+      <c r="B99" s="64" t="n"/>
+      <c r="C99" s="64" t="n"/>
+      <c r="D99" s="64" t="n"/>
+      <c r="E99" s="64" t="n"/>
       <c r="F99" s="64" t="n"/>
       <c r="G99" s="64" t="n"/>
       <c r="H99" s="64" t="n"/>
@@ -2149,10 +2149,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B100" s="19" t="n"/>
-      <c r="C100" s="65" t="n"/>
-      <c r="D100" s="65" t="n"/>
-      <c r="E100" s="19" t="n"/>
+      <c r="B100" s="64" t="n"/>
+      <c r="C100" s="64" t="n"/>
+      <c r="D100" s="64" t="n"/>
+      <c r="E100" s="64" t="n"/>
       <c r="F100" s="64" t="n"/>
       <c r="G100" s="64" t="n"/>
       <c r="H100" s="64" t="n"/>
@@ -2163,10 +2163,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B101" s="19" t="n"/>
-      <c r="C101" s="65" t="n"/>
-      <c r="D101" s="65" t="n"/>
-      <c r="E101" s="19" t="n"/>
+      <c r="B101" s="64" t="n"/>
+      <c r="C101" s="64" t="n"/>
+      <c r="D101" s="64" t="n"/>
+      <c r="E101" s="64" t="n"/>
       <c r="F101" s="64" t="n"/>
       <c r="G101" s="64" t="n"/>
       <c r="H101" s="64" t="n"/>
@@ -2177,10 +2177,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B102" s="19" t="n"/>
-      <c r="C102" s="65" t="n"/>
-      <c r="D102" s="65" t="n"/>
-      <c r="E102" s="19" t="n"/>
+      <c r="B102" s="64" t="n"/>
+      <c r="C102" s="64" t="n"/>
+      <c r="D102" s="64" t="n"/>
+      <c r="E102" s="64" t="n"/>
       <c r="F102" s="64" t="n"/>
       <c r="G102" s="64" t="n"/>
       <c r="H102" s="64" t="n"/>
@@ -2191,10 +2191,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B103" s="19" t="n"/>
-      <c r="C103" s="65" t="n"/>
-      <c r="D103" s="65" t="n"/>
-      <c r="E103" s="19" t="n"/>
+      <c r="B103" s="64" t="n"/>
+      <c r="C103" s="64" t="n"/>
+      <c r="D103" s="64" t="n"/>
+      <c r="E103" s="64" t="n"/>
       <c r="F103" s="64" t="n"/>
       <c r="G103" s="64" t="n"/>
       <c r="H103" s="64" t="n"/>
@@ -2205,10 +2205,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B104" s="19" t="n"/>
-      <c r="C104" s="65" t="n"/>
-      <c r="D104" s="65" t="n"/>
-      <c r="E104" s="19" t="n"/>
+      <c r="B104" s="64" t="n"/>
+      <c r="C104" s="64" t="n"/>
+      <c r="D104" s="64" t="n"/>
+      <c r="E104" s="64" t="n"/>
       <c r="F104" s="64" t="n"/>
       <c r="G104" s="64" t="n"/>
       <c r="H104" s="64" t="n"/>
@@ -2219,10 +2219,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B105" s="19" t="n"/>
-      <c r="C105" s="65" t="n"/>
-      <c r="D105" s="65" t="n"/>
-      <c r="E105" s="19" t="n"/>
+      <c r="B105" s="64" t="n"/>
+      <c r="C105" s="64" t="n"/>
+      <c r="D105" s="64" t="n"/>
+      <c r="E105" s="64" t="n"/>
       <c r="F105" s="64" t="n"/>
       <c r="G105" s="64" t="n"/>
       <c r="H105" s="64" t="n"/>
@@ -2233,10 +2233,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B106" s="19" t="n"/>
-      <c r="C106" s="65" t="n"/>
-      <c r="D106" s="65" t="n"/>
-      <c r="E106" s="19" t="n"/>
+      <c r="B106" s="64" t="n"/>
+      <c r="C106" s="64" t="n"/>
+      <c r="D106" s="64" t="n"/>
+      <c r="E106" s="64" t="n"/>
       <c r="F106" s="64" t="n"/>
       <c r="G106" s="64" t="n"/>
       <c r="H106" s="64" t="n"/>
@@ -2247,10 +2247,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B107" s="19" t="n"/>
-      <c r="C107" s="65" t="n"/>
-      <c r="D107" s="65" t="n"/>
-      <c r="E107" s="19" t="n"/>
+      <c r="B107" s="64" t="n"/>
+      <c r="C107" s="64" t="n"/>
+      <c r="D107" s="64" t="n"/>
+      <c r="E107" s="64" t="n"/>
       <c r="F107" s="64" t="n"/>
       <c r="G107" s="64" t="n"/>
       <c r="H107" s="64" t="n"/>
@@ -2261,10 +2261,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B108" s="19" t="n"/>
-      <c r="C108" s="65" t="n"/>
-      <c r="D108" s="65" t="n"/>
-      <c r="E108" s="19" t="n"/>
+      <c r="B108" s="64" t="n"/>
+      <c r="C108" s="64" t="n"/>
+      <c r="D108" s="64" t="n"/>
+      <c r="E108" s="64" t="n"/>
       <c r="F108" s="64" t="n"/>
       <c r="G108" s="64" t="n"/>
       <c r="H108" s="64" t="n"/>
@@ -2275,10 +2275,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B109" s="19" t="n"/>
-      <c r="C109" s="65" t="n"/>
-      <c r="D109" s="65" t="n"/>
-      <c r="E109" s="19" t="n"/>
+      <c r="B109" s="64" t="n"/>
+      <c r="C109" s="64" t="n"/>
+      <c r="D109" s="64" t="n"/>
+      <c r="E109" s="64" t="n"/>
       <c r="F109" s="64" t="n"/>
       <c r="G109" s="64" t="n"/>
       <c r="H109" s="64" t="n"/>
@@ -2289,10 +2289,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B110" s="19" t="n"/>
-      <c r="C110" s="65" t="n"/>
-      <c r="D110" s="65" t="n"/>
-      <c r="E110" s="19" t="n"/>
+      <c r="B110" s="64" t="n"/>
+      <c r="C110" s="64" t="n"/>
+      <c r="D110" s="64" t="n"/>
+      <c r="E110" s="64" t="n"/>
       <c r="F110" s="64" t="n"/>
       <c r="G110" s="64" t="n"/>
       <c r="H110" s="64" t="n"/>
@@ -2303,10 +2303,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B111" s="19" t="n"/>
-      <c r="C111" s="65" t="n"/>
-      <c r="D111" s="65" t="n"/>
-      <c r="E111" s="19" t="n"/>
+      <c r="B111" s="64" t="n"/>
+      <c r="C111" s="64" t="n"/>
+      <c r="D111" s="64" t="n"/>
+      <c r="E111" s="64" t="n"/>
       <c r="F111" s="64" t="n"/>
       <c r="G111" s="64" t="n"/>
       <c r="H111" s="64" t="n"/>
@@ -2317,10 +2317,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B112" s="19" t="n"/>
-      <c r="C112" s="65" t="n"/>
-      <c r="D112" s="65" t="n"/>
-      <c r="E112" s="19" t="n"/>
+      <c r="B112" s="64" t="n"/>
+      <c r="C112" s="64" t="n"/>
+      <c r="D112" s="64" t="n"/>
+      <c r="E112" s="64" t="n"/>
       <c r="F112" s="64" t="n"/>
       <c r="G112" s="64" t="n"/>
       <c r="H112" s="64" t="n"/>
@@ -2331,10 +2331,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B113" s="19" t="n"/>
-      <c r="C113" s="65" t="n"/>
-      <c r="D113" s="65" t="n"/>
-      <c r="E113" s="19" t="n"/>
+      <c r="B113" s="64" t="n"/>
+      <c r="C113" s="64" t="n"/>
+      <c r="D113" s="64" t="n"/>
+      <c r="E113" s="64" t="n"/>
       <c r="F113" s="64" t="n"/>
       <c r="G113" s="64" t="n"/>
       <c r="H113" s="64" t="n"/>
@@ -2345,10 +2345,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B114" s="19" t="n"/>
-      <c r="C114" s="65" t="n"/>
-      <c r="D114" s="65" t="n"/>
-      <c r="E114" s="19" t="n"/>
+      <c r="B114" s="64" t="n"/>
+      <c r="C114" s="64" t="n"/>
+      <c r="D114" s="64" t="n"/>
+      <c r="E114" s="64" t="n"/>
       <c r="F114" s="64" t="n"/>
       <c r="G114" s="64" t="n"/>
       <c r="H114" s="64" t="n"/>
@@ -2359,10 +2359,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B115" s="19" t="n"/>
-      <c r="C115" s="65" t="n"/>
-      <c r="D115" s="65" t="n"/>
-      <c r="E115" s="19" t="n"/>
+      <c r="B115" s="64" t="n"/>
+      <c r="C115" s="64" t="n"/>
+      <c r="D115" s="64" t="n"/>
+      <c r="E115" s="64" t="n"/>
       <c r="F115" s="64" t="n"/>
       <c r="G115" s="64" t="n"/>
       <c r="H115" s="64" t="n"/>
@@ -2373,10 +2373,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B116" s="19" t="n"/>
-      <c r="C116" s="65" t="n"/>
-      <c r="D116" s="65" t="n"/>
-      <c r="E116" s="19" t="n"/>
+      <c r="B116" s="64" t="n"/>
+      <c r="C116" s="64" t="n"/>
+      <c r="D116" s="64" t="n"/>
+      <c r="E116" s="64" t="n"/>
       <c r="F116" s="64" t="n"/>
       <c r="G116" s="64" t="n"/>
       <c r="H116" s="64" t="n"/>
@@ -2387,10 +2387,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B117" s="19" t="n"/>
-      <c r="C117" s="65" t="n"/>
-      <c r="D117" s="65" t="n"/>
-      <c r="E117" s="19" t="n"/>
+      <c r="B117" s="64" t="n"/>
+      <c r="C117" s="64" t="n"/>
+      <c r="D117" s="64" t="n"/>
+      <c r="E117" s="64" t="n"/>
       <c r="F117" s="64" t="n"/>
       <c r="G117" s="64" t="n"/>
       <c r="H117" s="64" t="n"/>
@@ -2401,10 +2401,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B118" s="19" t="n"/>
-      <c r="C118" s="65" t="n"/>
-      <c r="D118" s="65" t="n"/>
-      <c r="E118" s="19" t="n"/>
+      <c r="B118" s="64" t="n"/>
+      <c r="C118" s="64" t="n"/>
+      <c r="D118" s="64" t="n"/>
+      <c r="E118" s="64" t="n"/>
       <c r="F118" s="64" t="n"/>
       <c r="G118" s="64" t="n"/>
       <c r="H118" s="64" t="n"/>
@@ -2415,10 +2415,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B119" s="19" t="n"/>
-      <c r="C119" s="65" t="n"/>
-      <c r="D119" s="65" t="n"/>
-      <c r="E119" s="19" t="n"/>
+      <c r="B119" s="64" t="n"/>
+      <c r="C119" s="64" t="n"/>
+      <c r="D119" s="64" t="n"/>
+      <c r="E119" s="64" t="n"/>
       <c r="F119" s="64" t="n"/>
       <c r="G119" s="64" t="n"/>
       <c r="H119" s="64" t="n"/>
@@ -2429,10 +2429,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B120" s="19" t="n"/>
-      <c r="C120" s="65" t="n"/>
-      <c r="D120" s="65" t="n"/>
-      <c r="E120" s="19" t="n"/>
+      <c r="B120" s="64" t="n"/>
+      <c r="C120" s="64" t="n"/>
+      <c r="D120" s="64" t="n"/>
+      <c r="E120" s="64" t="n"/>
       <c r="F120" s="64" t="n"/>
       <c r="G120" s="64" t="n"/>
       <c r="H120" s="64" t="n"/>
@@ -2443,10 +2443,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B121" s="19" t="n"/>
-      <c r="C121" s="65" t="n"/>
-      <c r="D121" s="65" t="n"/>
-      <c r="E121" s="19" t="n"/>
+      <c r="B121" s="64" t="n"/>
+      <c r="C121" s="64" t="n"/>
+      <c r="D121" s="64" t="n"/>
+      <c r="E121" s="64" t="n"/>
       <c r="F121" s="64" t="n"/>
       <c r="G121" s="64" t="n"/>
       <c r="H121" s="64" t="n"/>
@@ -2457,10 +2457,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B122" s="19" t="n"/>
-      <c r="C122" s="65" t="n"/>
-      <c r="D122" s="65" t="n"/>
-      <c r="E122" s="19" t="n"/>
+      <c r="B122" s="64" t="n"/>
+      <c r="C122" s="64" t="n"/>
+      <c r="D122" s="64" t="n"/>
+      <c r="E122" s="64" t="n"/>
       <c r="F122" s="64" t="n"/>
       <c r="G122" s="64" t="n"/>
       <c r="H122" s="64" t="n"/>
@@ -2471,10 +2471,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B123" s="19" t="n"/>
-      <c r="C123" s="65" t="n"/>
-      <c r="D123" s="65" t="n"/>
-      <c r="E123" s="19" t="n"/>
+      <c r="B123" s="64" t="n"/>
+      <c r="C123" s="64" t="n"/>
+      <c r="D123" s="64" t="n"/>
+      <c r="E123" s="64" t="n"/>
       <c r="F123" s="64" t="n"/>
       <c r="G123" s="64" t="n"/>
       <c r="H123" s="64" t="n"/>
@@ -2485,10 +2485,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B124" s="19" t="n"/>
-      <c r="C124" s="65" t="n"/>
-      <c r="D124" s="65" t="n"/>
-      <c r="E124" s="19" t="n"/>
+      <c r="B124" s="64" t="n"/>
+      <c r="C124" s="64" t="n"/>
+      <c r="D124" s="64" t="n"/>
+      <c r="E124" s="64" t="n"/>
       <c r="F124" s="64" t="n"/>
       <c r="G124" s="64" t="n"/>
       <c r="H124" s="64" t="n"/>
@@ -2499,10 +2499,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B125" s="19" t="n"/>
-      <c r="C125" s="65" t="n"/>
-      <c r="D125" s="65" t="n"/>
-      <c r="E125" s="19" t="n"/>
+      <c r="B125" s="64" t="n"/>
+      <c r="C125" s="64" t="n"/>
+      <c r="D125" s="64" t="n"/>
+      <c r="E125" s="64" t="n"/>
       <c r="F125" s="64" t="n"/>
       <c r="G125" s="64" t="n"/>
       <c r="H125" s="64" t="n"/>
@@ -2513,10 +2513,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B126" s="19" t="n"/>
-      <c r="C126" s="65" t="n"/>
-      <c r="D126" s="65" t="n"/>
-      <c r="E126" s="19" t="n"/>
+      <c r="B126" s="64" t="n"/>
+      <c r="C126" s="64" t="n"/>
+      <c r="D126" s="64" t="n"/>
+      <c r="E126" s="64" t="n"/>
       <c r="F126" s="64" t="n"/>
       <c r="G126" s="64" t="n"/>
       <c r="H126" s="64" t="n"/>
@@ -2527,10 +2527,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B127" s="19" t="n"/>
-      <c r="C127" s="65" t="n"/>
-      <c r="D127" s="65" t="n"/>
-      <c r="E127" s="19" t="n"/>
+      <c r="B127" s="64" t="n"/>
+      <c r="C127" s="64" t="n"/>
+      <c r="D127" s="64" t="n"/>
+      <c r="E127" s="64" t="n"/>
       <c r="F127" s="64" t="n"/>
       <c r="G127" s="64" t="n"/>
       <c r="H127" s="64" t="n"/>
@@ -2541,10 +2541,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B128" s="19" t="n"/>
-      <c r="C128" s="65" t="n"/>
-      <c r="D128" s="65" t="n"/>
-      <c r="E128" s="19" t="n"/>
+      <c r="B128" s="64" t="n"/>
+      <c r="C128" s="64" t="n"/>
+      <c r="D128" s="64" t="n"/>
+      <c r="E128" s="64" t="n"/>
       <c r="F128" s="64" t="n"/>
       <c r="G128" s="64" t="n"/>
       <c r="H128" s="64" t="n"/>
@@ -2555,10 +2555,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B129" s="19" t="n"/>
-      <c r="C129" s="65" t="n"/>
-      <c r="D129" s="65" t="n"/>
-      <c r="E129" s="19" t="n"/>
+      <c r="B129" s="64" t="n"/>
+      <c r="C129" s="64" t="n"/>
+      <c r="D129" s="64" t="n"/>
+      <c r="E129" s="64" t="n"/>
       <c r="F129" s="64" t="n"/>
       <c r="G129" s="64" t="n"/>
       <c r="H129" s="64" t="n"/>
@@ -2569,10 +2569,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B130" s="19" t="n"/>
-      <c r="C130" s="65" t="n"/>
-      <c r="D130" s="65" t="n"/>
-      <c r="E130" s="19" t="n"/>
+      <c r="B130" s="64" t="n"/>
+      <c r="C130" s="64" t="n"/>
+      <c r="D130" s="64" t="n"/>
+      <c r="E130" s="64" t="n"/>
       <c r="F130" s="64" t="n"/>
       <c r="G130" s="64" t="n"/>
       <c r="H130" s="64" t="n"/>
@@ -2583,10 +2583,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B131" s="19" t="n"/>
-      <c r="C131" s="65" t="n"/>
-      <c r="D131" s="65" t="n"/>
-      <c r="E131" s="19" t="n"/>
+      <c r="B131" s="64" t="n"/>
+      <c r="C131" s="64" t="n"/>
+      <c r="D131" s="64" t="n"/>
+      <c r="E131" s="64" t="n"/>
       <c r="F131" s="64" t="n"/>
       <c r="G131" s="64" t="n"/>
       <c r="H131" s="64" t="n"/>
@@ -2597,10 +2597,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B132" s="19" t="n"/>
-      <c r="C132" s="65" t="n"/>
-      <c r="D132" s="65" t="n"/>
-      <c r="E132" s="19" t="n"/>
+      <c r="B132" s="64" t="n"/>
+      <c r="C132" s="64" t="n"/>
+      <c r="D132" s="64" t="n"/>
+      <c r="E132" s="64" t="n"/>
       <c r="F132" s="64" t="n"/>
       <c r="G132" s="64" t="n"/>
       <c r="H132" s="64" t="n"/>
@@ -2611,10 +2611,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B133" s="19" t="n"/>
-      <c r="C133" s="65" t="n"/>
-      <c r="D133" s="65" t="n"/>
-      <c r="E133" s="19" t="n"/>
+      <c r="B133" s="64" t="n"/>
+      <c r="C133" s="64" t="n"/>
+      <c r="D133" s="64" t="n"/>
+      <c r="E133" s="64" t="n"/>
       <c r="F133" s="64" t="n"/>
       <c r="G133" s="64" t="n"/>
       <c r="H133" s="64" t="n"/>
@@ -2625,10 +2625,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B134" s="19" t="n"/>
-      <c r="C134" s="65" t="n"/>
-      <c r="D134" s="65" t="n"/>
-      <c r="E134" s="19" t="n"/>
+      <c r="B134" s="64" t="n"/>
+      <c r="C134" s="64" t="n"/>
+      <c r="D134" s="64" t="n"/>
+      <c r="E134" s="64" t="n"/>
       <c r="F134" s="64" t="n"/>
       <c r="G134" s="64" t="n"/>
       <c r="H134" s="64" t="n"/>
@@ -2639,10 +2639,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B135" s="19" t="n"/>
-      <c r="C135" s="65" t="n"/>
-      <c r="D135" s="65" t="n"/>
-      <c r="E135" s="19" t="n"/>
+      <c r="B135" s="64" t="n"/>
+      <c r="C135" s="64" t="n"/>
+      <c r="D135" s="64" t="n"/>
+      <c r="E135" s="64" t="n"/>
       <c r="F135" s="64" t="n"/>
       <c r="G135" s="64" t="n"/>
       <c r="H135" s="64" t="n"/>
@@ -2653,10 +2653,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B136" s="19" t="n"/>
-      <c r="C136" s="65" t="n"/>
-      <c r="D136" s="65" t="n"/>
-      <c r="E136" s="19" t="n"/>
+      <c r="B136" s="64" t="n"/>
+      <c r="C136" s="64" t="n"/>
+      <c r="D136" s="64" t="n"/>
+      <c r="E136" s="64" t="n"/>
       <c r="F136" s="64" t="n"/>
       <c r="G136" s="64" t="n"/>
       <c r="H136" s="64" t="n"/>
@@ -2667,10 +2667,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B137" s="19" t="n"/>
-      <c r="C137" s="65" t="n"/>
-      <c r="D137" s="65" t="n"/>
-      <c r="E137" s="19" t="n"/>
+      <c r="B137" s="64" t="n"/>
+      <c r="C137" s="64" t="n"/>
+      <c r="D137" s="64" t="n"/>
+      <c r="E137" s="64" t="n"/>
       <c r="F137" s="64" t="n"/>
       <c r="G137" s="64" t="n"/>
       <c r="H137" s="64" t="n"/>
@@ -2681,10 +2681,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B138" s="19" t="n"/>
-      <c r="C138" s="65" t="n"/>
-      <c r="D138" s="65" t="n"/>
-      <c r="E138" s="19" t="n"/>
+      <c r="B138" s="64" t="n"/>
+      <c r="C138" s="64" t="n"/>
+      <c r="D138" s="64" t="n"/>
+      <c r="E138" s="64" t="n"/>
       <c r="F138" s="64" t="n"/>
       <c r="G138" s="64" t="n"/>
       <c r="H138" s="64" t="n"/>
@@ -2695,10 +2695,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B139" s="19" t="n"/>
-      <c r="C139" s="65" t="n"/>
-      <c r="D139" s="65" t="n"/>
-      <c r="E139" s="19" t="n"/>
+      <c r="B139" s="64" t="n"/>
+      <c r="C139" s="64" t="n"/>
+      <c r="D139" s="64" t="n"/>
+      <c r="E139" s="64" t="n"/>
       <c r="F139" s="64" t="n"/>
       <c r="G139" s="64" t="n"/>
       <c r="H139" s="64" t="n"/>
@@ -2709,10 +2709,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B140" s="19" t="n"/>
-      <c r="C140" s="65" t="n"/>
-      <c r="D140" s="65" t="n"/>
-      <c r="E140" s="19" t="n"/>
+      <c r="B140" s="64" t="n"/>
+      <c r="C140" s="64" t="n"/>
+      <c r="D140" s="64" t="n"/>
+      <c r="E140" s="64" t="n"/>
       <c r="F140" s="64" t="n"/>
       <c r="G140" s="64" t="n"/>
       <c r="H140" s="64" t="n"/>
@@ -2723,10 +2723,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B141" s="19" t="n"/>
-      <c r="C141" s="65" t="n"/>
-      <c r="D141" s="65" t="n"/>
-      <c r="E141" s="19" t="n"/>
+      <c r="B141" s="64" t="n"/>
+      <c r="C141" s="64" t="n"/>
+      <c r="D141" s="64" t="n"/>
+      <c r="E141" s="64" t="n"/>
       <c r="F141" s="64" t="n"/>
       <c r="G141" s="64" t="n"/>
       <c r="H141" s="64" t="n"/>
@@ -2737,10 +2737,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B142" s="19" t="n"/>
-      <c r="C142" s="65" t="n"/>
-      <c r="D142" s="65" t="n"/>
-      <c r="E142" s="19" t="n"/>
+      <c r="B142" s="64" t="n"/>
+      <c r="C142" s="64" t="n"/>
+      <c r="D142" s="64" t="n"/>
+      <c r="E142" s="64" t="n"/>
       <c r="F142" s="64" t="n"/>
       <c r="G142" s="64" t="n"/>
       <c r="H142" s="64" t="n"/>
@@ -2751,10 +2751,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B143" s="19" t="n"/>
-      <c r="C143" s="65" t="n"/>
-      <c r="D143" s="65" t="n"/>
-      <c r="E143" s="19" t="n"/>
+      <c r="B143" s="64" t="n"/>
+      <c r="C143" s="64" t="n"/>
+      <c r="D143" s="64" t="n"/>
+      <c r="E143" s="64" t="n"/>
       <c r="F143" s="64" t="n"/>
       <c r="G143" s="64" t="n"/>
       <c r="H143" s="64" t="n"/>
@@ -2765,10 +2765,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B144" s="19" t="n"/>
-      <c r="C144" s="65" t="n"/>
-      <c r="D144" s="65" t="n"/>
-      <c r="E144" s="19" t="n"/>
+      <c r="B144" s="64" t="n"/>
+      <c r="C144" s="64" t="n"/>
+      <c r="D144" s="64" t="n"/>
+      <c r="E144" s="64" t="n"/>
       <c r="F144" s="64" t="n"/>
       <c r="G144" s="64" t="n"/>
       <c r="H144" s="64" t="n"/>
@@ -2779,10 +2779,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B145" s="19" t="n"/>
-      <c r="C145" s="65" t="n"/>
-      <c r="D145" s="65" t="n"/>
-      <c r="E145" s="19" t="n"/>
+      <c r="B145" s="64" t="n"/>
+      <c r="C145" s="64" t="n"/>
+      <c r="D145" s="64" t="n"/>
+      <c r="E145" s="64" t="n"/>
       <c r="F145" s="64" t="n"/>
       <c r="G145" s="64" t="n"/>
       <c r="H145" s="64" t="n"/>
@@ -2793,10 +2793,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B146" s="19" t="n"/>
-      <c r="C146" s="65" t="n"/>
-      <c r="D146" s="65" t="n"/>
-      <c r="E146" s="19" t="n"/>
+      <c r="B146" s="64" t="n"/>
+      <c r="C146" s="64" t="n"/>
+      <c r="D146" s="64" t="n"/>
+      <c r="E146" s="64" t="n"/>
       <c r="F146" s="64" t="n"/>
       <c r="G146" s="64" t="n"/>
       <c r="H146" s="64" t="n"/>
@@ -2807,10 +2807,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B147" s="19" t="n"/>
-      <c r="C147" s="65" t="n"/>
-      <c r="D147" s="65" t="n"/>
-      <c r="E147" s="19" t="n"/>
+      <c r="B147" s="64" t="n"/>
+      <c r="C147" s="64" t="n"/>
+      <c r="D147" s="64" t="n"/>
+      <c r="E147" s="64" t="n"/>
       <c r="F147" s="64" t="n"/>
       <c r="G147" s="64" t="n"/>
       <c r="H147" s="64" t="n"/>
@@ -2821,10 +2821,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B148" s="19" t="n"/>
-      <c r="C148" s="65" t="n"/>
-      <c r="D148" s="65" t="n"/>
-      <c r="E148" s="19" t="n"/>
+      <c r="B148" s="64" t="n"/>
+      <c r="C148" s="64" t="n"/>
+      <c r="D148" s="64" t="n"/>
+      <c r="E148" s="64" t="n"/>
       <c r="F148" s="64" t="n"/>
       <c r="G148" s="64" t="n"/>
       <c r="H148" s="64" t="n"/>
@@ -2835,10 +2835,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B149" s="19" t="n"/>
-      <c r="C149" s="65" t="n"/>
-      <c r="D149" s="65" t="n"/>
-      <c r="E149" s="19" t="n"/>
+      <c r="B149" s="64" t="n"/>
+      <c r="C149" s="64" t="n"/>
+      <c r="D149" s="64" t="n"/>
+      <c r="E149" s="64" t="n"/>
       <c r="F149" s="64" t="n"/>
       <c r="G149" s="64" t="n"/>
       <c r="H149" s="64" t="n"/>
@@ -2849,10 +2849,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B150" s="19" t="n"/>
-      <c r="C150" s="65" t="n"/>
-      <c r="D150" s="65" t="n"/>
-      <c r="E150" s="19" t="n"/>
+      <c r="B150" s="64" t="n"/>
+      <c r="C150" s="64" t="n"/>
+      <c r="D150" s="64" t="n"/>
+      <c r="E150" s="64" t="n"/>
       <c r="F150" s="64" t="n"/>
       <c r="G150" s="64" t="n"/>
       <c r="H150" s="64" t="n"/>
@@ -2863,10 +2863,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B151" s="19" t="n"/>
-      <c r="C151" s="65" t="n"/>
-      <c r="D151" s="65" t="n"/>
-      <c r="E151" s="19" t="n"/>
+      <c r="B151" s="64" t="n"/>
+      <c r="C151" s="64" t="n"/>
+      <c r="D151" s="64" t="n"/>
+      <c r="E151" s="64" t="n"/>
       <c r="F151" s="64" t="n"/>
       <c r="G151" s="64" t="n"/>
       <c r="H151" s="64" t="n"/>
@@ -2877,10 +2877,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B152" s="19" t="n"/>
-      <c r="C152" s="65" t="n"/>
-      <c r="D152" s="65" t="n"/>
-      <c r="E152" s="19" t="n"/>
+      <c r="B152" s="64" t="n"/>
+      <c r="C152" s="64" t="n"/>
+      <c r="D152" s="64" t="n"/>
+      <c r="E152" s="64" t="n"/>
       <c r="F152" s="64" t="n"/>
       <c r="G152" s="64" t="n"/>
       <c r="H152" s="64" t="n"/>
@@ -2891,10 +2891,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B153" s="19" t="n"/>
-      <c r="C153" s="65" t="n"/>
-      <c r="D153" s="65" t="n"/>
-      <c r="E153" s="19" t="n"/>
+      <c r="B153" s="64" t="n"/>
+      <c r="C153" s="64" t="n"/>
+      <c r="D153" s="64" t="n"/>
+      <c r="E153" s="64" t="n"/>
       <c r="F153" s="64" t="n"/>
       <c r="G153" s="64" t="n"/>
       <c r="H153" s="64" t="n"/>
@@ -2905,10 +2905,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B154" s="19" t="n"/>
-      <c r="C154" s="65" t="n"/>
-      <c r="D154" s="65" t="n"/>
-      <c r="E154" s="19" t="n"/>
+      <c r="B154" s="64" t="n"/>
+      <c r="C154" s="64" t="n"/>
+      <c r="D154" s="64" t="n"/>
+      <c r="E154" s="64" t="n"/>
       <c r="F154" s="64" t="n"/>
       <c r="G154" s="64" t="n"/>
       <c r="H154" s="64" t="n"/>
@@ -2919,10 +2919,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B155" s="19" t="n"/>
-      <c r="C155" s="65" t="n"/>
-      <c r="D155" s="65" t="n"/>
-      <c r="E155" s="19" t="n"/>
+      <c r="B155" s="64" t="n"/>
+      <c r="C155" s="64" t="n"/>
+      <c r="D155" s="64" t="n"/>
+      <c r="E155" s="64" t="n"/>
       <c r="F155" s="64" t="n"/>
       <c r="G155" s="64" t="n"/>
       <c r="H155" s="64" t="n"/>
@@ -2933,10 +2933,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B156" s="19" t="n"/>
-      <c r="C156" s="65" t="n"/>
-      <c r="D156" s="65" t="n"/>
-      <c r="E156" s="19" t="n"/>
+      <c r="B156" s="64" t="n"/>
+      <c r="C156" s="64" t="n"/>
+      <c r="D156" s="64" t="n"/>
+      <c r="E156" s="64" t="n"/>
       <c r="F156" s="64" t="n"/>
       <c r="G156" s="64" t="n"/>
       <c r="H156" s="64" t="n"/>
@@ -2947,10 +2947,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B157" s="19" t="n"/>
-      <c r="C157" s="65" t="n"/>
-      <c r="D157" s="65" t="n"/>
-      <c r="E157" s="19" t="n"/>
+      <c r="B157" s="64" t="n"/>
+      <c r="C157" s="64" t="n"/>
+      <c r="D157" s="64" t="n"/>
+      <c r="E157" s="64" t="n"/>
       <c r="F157" s="64" t="n"/>
       <c r="G157" s="64" t="n"/>
       <c r="H157" s="64" t="n"/>
@@ -2961,10 +2961,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B158" s="19" t="n"/>
-      <c r="C158" s="65" t="n"/>
-      <c r="D158" s="65" t="n"/>
-      <c r="E158" s="19" t="n"/>
+      <c r="B158" s="64" t="n"/>
+      <c r="C158" s="64" t="n"/>
+      <c r="D158" s="64" t="n"/>
+      <c r="E158" s="64" t="n"/>
       <c r="F158" s="64" t="n"/>
       <c r="G158" s="64" t="n"/>
       <c r="H158" s="64" t="n"/>
@@ -2975,10 +2975,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B159" s="19" t="n"/>
-      <c r="C159" s="65" t="n"/>
-      <c r="D159" s="65" t="n"/>
-      <c r="E159" s="19" t="n"/>
+      <c r="B159" s="64" t="n"/>
+      <c r="C159" s="64" t="n"/>
+      <c r="D159" s="64" t="n"/>
+      <c r="E159" s="64" t="n"/>
       <c r="F159" s="64" t="n"/>
       <c r="G159" s="64" t="n"/>
       <c r="H159" s="64" t="n"/>
@@ -2989,10 +2989,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B160" s="19" t="n"/>
-      <c r="C160" s="65" t="n"/>
-      <c r="D160" s="65" t="n"/>
-      <c r="E160" s="19" t="n"/>
+      <c r="B160" s="64" t="n"/>
+      <c r="C160" s="64" t="n"/>
+      <c r="D160" s="64" t="n"/>
+      <c r="E160" s="64" t="n"/>
       <c r="F160" s="64" t="n"/>
       <c r="G160" s="64" t="n"/>
       <c r="H160" s="64" t="n"/>
@@ -3003,10 +3003,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B161" s="19" t="n"/>
-      <c r="C161" s="65" t="n"/>
-      <c r="D161" s="65" t="n"/>
-      <c r="E161" s="19" t="n"/>
+      <c r="B161" s="64" t="n"/>
+      <c r="C161" s="64" t="n"/>
+      <c r="D161" s="64" t="n"/>
+      <c r="E161" s="64" t="n"/>
       <c r="F161" s="64" t="n"/>
       <c r="G161" s="64" t="n"/>
       <c r="H161" s="64" t="n"/>
@@ -3017,10 +3017,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B162" s="19" t="n"/>
-      <c r="C162" s="65" t="n"/>
-      <c r="D162" s="65" t="n"/>
-      <c r="E162" s="19" t="n"/>
+      <c r="B162" s="64" t="n"/>
+      <c r="C162" s="64" t="n"/>
+      <c r="D162" s="64" t="n"/>
+      <c r="E162" s="64" t="n"/>
       <c r="F162" s="64" t="n"/>
       <c r="G162" s="64" t="n"/>
       <c r="H162" s="64" t="n"/>
@@ -3031,10 +3031,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B163" s="19" t="n"/>
-      <c r="C163" s="65" t="n"/>
-      <c r="D163" s="65" t="n"/>
-      <c r="E163" s="19" t="n"/>
+      <c r="B163" s="64" t="n"/>
+      <c r="C163" s="64" t="n"/>
+      <c r="D163" s="64" t="n"/>
+      <c r="E163" s="64" t="n"/>
       <c r="F163" s="64" t="n"/>
       <c r="G163" s="64" t="n"/>
       <c r="H163" s="64" t="n"/>
@@ -3045,10 +3045,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B164" s="19" t="n"/>
-      <c r="C164" s="65" t="n"/>
-      <c r="D164" s="65" t="n"/>
-      <c r="E164" s="19" t="n"/>
+      <c r="B164" s="64" t="n"/>
+      <c r="C164" s="64" t="n"/>
+      <c r="D164" s="64" t="n"/>
+      <c r="E164" s="64" t="n"/>
       <c r="F164" s="64" t="n"/>
       <c r="G164" s="64" t="n"/>
       <c r="H164" s="64" t="n"/>
@@ -3059,10 +3059,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B165" s="19" t="n"/>
-      <c r="C165" s="65" t="n"/>
-      <c r="D165" s="65" t="n"/>
-      <c r="E165" s="19" t="n"/>
+      <c r="B165" s="64" t="n"/>
+      <c r="C165" s="64" t="n"/>
+      <c r="D165" s="64" t="n"/>
+      <c r="E165" s="64" t="n"/>
       <c r="F165" s="64" t="n"/>
       <c r="G165" s="64" t="n"/>
       <c r="H165" s="64" t="n"/>
@@ -3073,10 +3073,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B166" s="19" t="n"/>
-      <c r="C166" s="65" t="n"/>
-      <c r="D166" s="65" t="n"/>
-      <c r="E166" s="19" t="n"/>
+      <c r="B166" s="64" t="n"/>
+      <c r="C166" s="64" t="n"/>
+      <c r="D166" s="64" t="n"/>
+      <c r="E166" s="64" t="n"/>
       <c r="F166" s="64" t="n"/>
       <c r="G166" s="64" t="n"/>
       <c r="H166" s="64" t="n"/>
@@ -3087,10 +3087,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B167" s="19" t="n"/>
-      <c r="C167" s="65" t="n"/>
-      <c r="D167" s="65" t="n"/>
-      <c r="E167" s="19" t="n"/>
+      <c r="B167" s="64" t="n"/>
+      <c r="C167" s="64" t="n"/>
+      <c r="D167" s="64" t="n"/>
+      <c r="E167" s="64" t="n"/>
       <c r="F167" s="64" t="n"/>
       <c r="G167" s="64" t="n"/>
       <c r="H167" s="64" t="n"/>
@@ -3101,10 +3101,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B168" s="19" t="n"/>
-      <c r="C168" s="65" t="n"/>
-      <c r="D168" s="65" t="n"/>
-      <c r="E168" s="19" t="n"/>
+      <c r="B168" s="64" t="n"/>
+      <c r="C168" s="64" t="n"/>
+      <c r="D168" s="64" t="n"/>
+      <c r="E168" s="64" t="n"/>
       <c r="F168" s="64" t="n"/>
       <c r="G168" s="64" t="n"/>
       <c r="H168" s="64" t="n"/>
@@ -3115,10 +3115,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B169" s="19" t="n"/>
-      <c r="C169" s="65" t="n"/>
-      <c r="D169" s="65" t="n"/>
-      <c r="E169" s="19" t="n"/>
+      <c r="B169" s="64" t="n"/>
+      <c r="C169" s="64" t="n"/>
+      <c r="D169" s="64" t="n"/>
+      <c r="E169" s="64" t="n"/>
       <c r="F169" s="64" t="n"/>
       <c r="G169" s="64" t="n"/>
       <c r="H169" s="64" t="n"/>
@@ -3129,10 +3129,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B170" s="19" t="n"/>
-      <c r="C170" s="65" t="n"/>
-      <c r="D170" s="65" t="n"/>
-      <c r="E170" s="19" t="n"/>
+      <c r="B170" s="64" t="n"/>
+      <c r="C170" s="64" t="n"/>
+      <c r="D170" s="64" t="n"/>
+      <c r="E170" s="64" t="n"/>
       <c r="F170" s="64" t="n"/>
       <c r="G170" s="64" t="n"/>
       <c r="H170" s="64" t="n"/>
@@ -3143,10 +3143,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B171" s="19" t="n"/>
-      <c r="C171" s="65" t="n"/>
-      <c r="D171" s="65" t="n"/>
-      <c r="E171" s="19" t="n"/>
+      <c r="B171" s="64" t="n"/>
+      <c r="C171" s="64" t="n"/>
+      <c r="D171" s="64" t="n"/>
+      <c r="E171" s="64" t="n"/>
       <c r="F171" s="64" t="n"/>
       <c r="G171" s="64" t="n"/>
       <c r="H171" s="64" t="n"/>
@@ -3157,10 +3157,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B172" s="19" t="n"/>
-      <c r="C172" s="65" t="n"/>
-      <c r="D172" s="65" t="n"/>
-      <c r="E172" s="19" t="n"/>
+      <c r="B172" s="64" t="n"/>
+      <c r="C172" s="64" t="n"/>
+      <c r="D172" s="64" t="n"/>
+      <c r="E172" s="64" t="n"/>
       <c r="F172" s="64" t="n"/>
       <c r="G172" s="64" t="n"/>
       <c r="H172" s="64" t="n"/>
@@ -3171,10 +3171,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B173" s="19" t="n"/>
-      <c r="C173" s="65" t="n"/>
-      <c r="D173" s="65" t="n"/>
-      <c r="E173" s="19" t="n"/>
+      <c r="B173" s="64" t="n"/>
+      <c r="C173" s="64" t="n"/>
+      <c r="D173" s="64" t="n"/>
+      <c r="E173" s="64" t="n"/>
       <c r="F173" s="64" t="n"/>
       <c r="G173" s="64" t="n"/>
       <c r="H173" s="64" t="n"/>
@@ -3185,10 +3185,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B174" s="19" t="n"/>
-      <c r="C174" s="65" t="n"/>
-      <c r="D174" s="65" t="n"/>
-      <c r="E174" s="19" t="n"/>
+      <c r="B174" s="64" t="n"/>
+      <c r="C174" s="64" t="n"/>
+      <c r="D174" s="64" t="n"/>
+      <c r="E174" s="64" t="n"/>
       <c r="F174" s="64" t="n"/>
       <c r="G174" s="64" t="n"/>
       <c r="H174" s="64" t="n"/>
@@ -3199,10 +3199,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B175" s="19" t="n"/>
-      <c r="C175" s="65" t="n"/>
-      <c r="D175" s="65" t="n"/>
-      <c r="E175" s="19" t="n"/>
+      <c r="B175" s="64" t="n"/>
+      <c r="C175" s="64" t="n"/>
+      <c r="D175" s="64" t="n"/>
+      <c r="E175" s="64" t="n"/>
       <c r="F175" s="64" t="n"/>
       <c r="G175" s="64" t="n"/>
       <c r="H175" s="64" t="n"/>
@@ -3213,10 +3213,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B176" s="19" t="n"/>
-      <c r="C176" s="65" t="n"/>
-      <c r="D176" s="65" t="n"/>
-      <c r="E176" s="19" t="n"/>
+      <c r="B176" s="64" t="n"/>
+      <c r="C176" s="64" t="n"/>
+      <c r="D176" s="64" t="n"/>
+      <c r="E176" s="64" t="n"/>
       <c r="F176" s="64" t="n"/>
       <c r="G176" s="64" t="n"/>
       <c r="H176" s="64" t="n"/>
@@ -3227,10 +3227,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B177" s="19" t="n"/>
-      <c r="C177" s="65" t="n"/>
-      <c r="D177" s="65" t="n"/>
-      <c r="E177" s="19" t="n"/>
+      <c r="B177" s="64" t="n"/>
+      <c r="C177" s="64" t="n"/>
+      <c r="D177" s="64" t="n"/>
+      <c r="E177" s="64" t="n"/>
       <c r="F177" s="64" t="n"/>
       <c r="G177" s="64" t="n"/>
       <c r="H177" s="64" t="n"/>
@@ -3241,10 +3241,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B178" s="19" t="n"/>
-      <c r="C178" s="65" t="n"/>
-      <c r="D178" s="65" t="n"/>
-      <c r="E178" s="19" t="n"/>
+      <c r="B178" s="64" t="n"/>
+      <c r="C178" s="64" t="n"/>
+      <c r="D178" s="64" t="n"/>
+      <c r="E178" s="64" t="n"/>
       <c r="F178" s="64" t="n"/>
       <c r="G178" s="64" t="n"/>
       <c r="H178" s="64" t="n"/>
@@ -3255,10 +3255,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B179" s="19" t="n"/>
-      <c r="C179" s="65" t="n"/>
-      <c r="D179" s="65" t="n"/>
-      <c r="E179" s="19" t="n"/>
+      <c r="B179" s="64" t="n"/>
+      <c r="C179" s="64" t="n"/>
+      <c r="D179" s="64" t="n"/>
+      <c r="E179" s="64" t="n"/>
       <c r="F179" s="64" t="n"/>
       <c r="G179" s="64" t="n"/>
       <c r="H179" s="64" t="n"/>
@@ -3269,10 +3269,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B180" s="19" t="n"/>
-      <c r="C180" s="65" t="n"/>
-      <c r="D180" s="65" t="n"/>
-      <c r="E180" s="19" t="n"/>
+      <c r="B180" s="64" t="n"/>
+      <c r="C180" s="64" t="n"/>
+      <c r="D180" s="64" t="n"/>
+      <c r="E180" s="64" t="n"/>
       <c r="F180" s="64" t="n"/>
       <c r="G180" s="64" t="n"/>
       <c r="H180" s="64" t="n"/>
@@ -3283,10 +3283,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B181" s="19" t="n"/>
-      <c r="C181" s="65" t="n"/>
-      <c r="D181" s="65" t="n"/>
-      <c r="E181" s="19" t="n"/>
+      <c r="B181" s="64" t="n"/>
+      <c r="C181" s="64" t="n"/>
+      <c r="D181" s="64" t="n"/>
+      <c r="E181" s="64" t="n"/>
       <c r="F181" s="64" t="n"/>
       <c r="G181" s="64" t="n"/>
       <c r="H181" s="64" t="n"/>
@@ -3297,10 +3297,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B182" s="19" t="n"/>
-      <c r="C182" s="65" t="n"/>
-      <c r="D182" s="65" t="n"/>
-      <c r="E182" s="19" t="n"/>
+      <c r="B182" s="64" t="n"/>
+      <c r="C182" s="64" t="n"/>
+      <c r="D182" s="64" t="n"/>
+      <c r="E182" s="64" t="n"/>
       <c r="F182" s="64" t="n"/>
       <c r="G182" s="64" t="n"/>
       <c r="H182" s="64" t="n"/>
@@ -3311,10 +3311,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B183" s="19" t="n"/>
-      <c r="C183" s="65" t="n"/>
-      <c r="D183" s="65" t="n"/>
-      <c r="E183" s="19" t="n"/>
+      <c r="B183" s="64" t="n"/>
+      <c r="C183" s="64" t="n"/>
+      <c r="D183" s="64" t="n"/>
+      <c r="E183" s="64" t="n"/>
       <c r="F183" s="64" t="n"/>
       <c r="G183" s="64" t="n"/>
       <c r="H183" s="64" t="n"/>
@@ -3325,10 +3325,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B184" s="19" t="n"/>
-      <c r="C184" s="65" t="n"/>
-      <c r="D184" s="65" t="n"/>
-      <c r="E184" s="19" t="n"/>
+      <c r="B184" s="64" t="n"/>
+      <c r="C184" s="64" t="n"/>
+      <c r="D184" s="64" t="n"/>
+      <c r="E184" s="64" t="n"/>
       <c r="F184" s="64" t="n"/>
       <c r="G184" s="64" t="n"/>
       <c r="H184" s="64" t="n"/>
@@ -3339,10 +3339,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B185" s="19" t="n"/>
-      <c r="C185" s="65" t="n"/>
-      <c r="D185" s="65" t="n"/>
-      <c r="E185" s="19" t="n"/>
+      <c r="B185" s="64" t="n"/>
+      <c r="C185" s="64" t="n"/>
+      <c r="D185" s="64" t="n"/>
+      <c r="E185" s="64" t="n"/>
       <c r="F185" s="64" t="n"/>
       <c r="G185" s="64" t="n"/>
       <c r="H185" s="64" t="n"/>
@@ -3353,10 +3353,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B186" s="19" t="n"/>
-      <c r="C186" s="65" t="n"/>
-      <c r="D186" s="65" t="n"/>
-      <c r="E186" s="19" t="n"/>
+      <c r="B186" s="64" t="n"/>
+      <c r="C186" s="64" t="n"/>
+      <c r="D186" s="64" t="n"/>
+      <c r="E186" s="64" t="n"/>
       <c r="F186" s="64" t="n"/>
       <c r="G186" s="64" t="n"/>
       <c r="H186" s="64" t="n"/>
@@ -3367,10 +3367,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B187" s="19" t="n"/>
-      <c r="C187" s="65" t="n"/>
-      <c r="D187" s="65" t="n"/>
-      <c r="E187" s="19" t="n"/>
+      <c r="B187" s="64" t="n"/>
+      <c r="C187" s="64" t="n"/>
+      <c r="D187" s="64" t="n"/>
+      <c r="E187" s="64" t="n"/>
       <c r="F187" s="64" t="n"/>
       <c r="G187" s="64" t="n"/>
       <c r="H187" s="64" t="n"/>
@@ -3381,10 +3381,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B188" s="19" t="n"/>
-      <c r="C188" s="65" t="n"/>
-      <c r="D188" s="65" t="n"/>
-      <c r="E188" s="19" t="n"/>
+      <c r="B188" s="64" t="n"/>
+      <c r="C188" s="64" t="n"/>
+      <c r="D188" s="64" t="n"/>
+      <c r="E188" s="64" t="n"/>
       <c r="F188" s="64" t="n"/>
       <c r="G188" s="64" t="n"/>
       <c r="H188" s="64" t="n"/>
@@ -3395,10 +3395,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B189" s="19" t="n"/>
-      <c r="C189" s="65" t="n"/>
-      <c r="D189" s="65" t="n"/>
-      <c r="E189" s="19" t="n"/>
+      <c r="B189" s="64" t="n"/>
+      <c r="C189" s="64" t="n"/>
+      <c r="D189" s="64" t="n"/>
+      <c r="E189" s="64" t="n"/>
       <c r="F189" s="64" t="n"/>
       <c r="G189" s="64" t="n"/>
       <c r="H189" s="64" t="n"/>
@@ -3409,10 +3409,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B190" s="19" t="n"/>
-      <c r="C190" s="65" t="n"/>
-      <c r="D190" s="65" t="n"/>
-      <c r="E190" s="19" t="n"/>
+      <c r="B190" s="64" t="n"/>
+      <c r="C190" s="64" t="n"/>
+      <c r="D190" s="64" t="n"/>
+      <c r="E190" s="64" t="n"/>
       <c r="F190" s="64" t="n"/>
       <c r="G190" s="64" t="n"/>
       <c r="H190" s="64" t="n"/>
@@ -3423,10 +3423,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B191" s="19" t="n"/>
-      <c r="C191" s="65" t="n"/>
-      <c r="D191" s="65" t="n"/>
-      <c r="E191" s="19" t="n"/>
+      <c r="B191" s="64" t="n"/>
+      <c r="C191" s="64" t="n"/>
+      <c r="D191" s="64" t="n"/>
+      <c r="E191" s="64" t="n"/>
       <c r="F191" s="64" t="n"/>
       <c r="G191" s="64" t="n"/>
       <c r="H191" s="64" t="n"/>
@@ -3437,10 +3437,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B192" s="19" t="n"/>
-      <c r="C192" s="65" t="n"/>
-      <c r="D192" s="65" t="n"/>
-      <c r="E192" s="19" t="n"/>
+      <c r="B192" s="64" t="n"/>
+      <c r="C192" s="64" t="n"/>
+      <c r="D192" s="64" t="n"/>
+      <c r="E192" s="64" t="n"/>
       <c r="F192" s="64" t="n"/>
       <c r="G192" s="64" t="n"/>
       <c r="H192" s="64" t="n"/>
@@ -3451,10 +3451,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B193" s="19" t="n"/>
-      <c r="C193" s="65" t="n"/>
-      <c r="D193" s="65" t="n"/>
-      <c r="E193" s="19" t="n"/>
+      <c r="B193" s="64" t="n"/>
+      <c r="C193" s="64" t="n"/>
+      <c r="D193" s="64" t="n"/>
+      <c r="E193" s="64" t="n"/>
       <c r="F193" s="64" t="n"/>
       <c r="G193" s="64" t="n"/>
       <c r="H193" s="64" t="n"/>
@@ -3465,10 +3465,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B194" s="19" t="n"/>
-      <c r="C194" s="65" t="n"/>
-      <c r="D194" s="65" t="n"/>
-      <c r="E194" s="19" t="n"/>
+      <c r="B194" s="64" t="n"/>
+      <c r="C194" s="64" t="n"/>
+      <c r="D194" s="64" t="n"/>
+      <c r="E194" s="64" t="n"/>
       <c r="F194" s="64" t="n"/>
       <c r="G194" s="64" t="n"/>
       <c r="H194" s="64" t="n"/>
@@ -3479,10 +3479,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B195" s="19" t="n"/>
-      <c r="C195" s="65" t="n"/>
-      <c r="D195" s="65" t="n"/>
-      <c r="E195" s="19" t="n"/>
+      <c r="B195" s="64" t="n"/>
+      <c r="C195" s="64" t="n"/>
+      <c r="D195" s="64" t="n"/>
+      <c r="E195" s="64" t="n"/>
       <c r="F195" s="64" t="n"/>
       <c r="G195" s="64" t="n"/>
       <c r="H195" s="64" t="n"/>
@@ -3493,10 +3493,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B196" s="19" t="n"/>
-      <c r="C196" s="65" t="n"/>
-      <c r="D196" s="65" t="n"/>
-      <c r="E196" s="19" t="n"/>
+      <c r="B196" s="64" t="n"/>
+      <c r="C196" s="64" t="n"/>
+      <c r="D196" s="64" t="n"/>
+      <c r="E196" s="64" t="n"/>
       <c r="F196" s="64" t="n"/>
       <c r="G196" s="64" t="n"/>
       <c r="H196" s="64" t="n"/>
@@ -3507,10 +3507,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B197" s="19" t="n"/>
-      <c r="C197" s="65" t="n"/>
-      <c r="D197" s="65" t="n"/>
-      <c r="E197" s="19" t="n"/>
+      <c r="B197" s="64" t="n"/>
+      <c r="C197" s="64" t="n"/>
+      <c r="D197" s="64" t="n"/>
+      <c r="E197" s="64" t="n"/>
       <c r="F197" s="64" t="n"/>
       <c r="G197" s="64" t="n"/>
       <c r="H197" s="64" t="n"/>
@@ -3521,10 +3521,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B198" s="19" t="n"/>
-      <c r="C198" s="65" t="n"/>
-      <c r="D198" s="65" t="n"/>
-      <c r="E198" s="19" t="n"/>
+      <c r="B198" s="64" t="n"/>
+      <c r="C198" s="64" t="n"/>
+      <c r="D198" s="64" t="n"/>
+      <c r="E198" s="64" t="n"/>
       <c r="F198" s="64" t="n"/>
       <c r="G198" s="64" t="n"/>
       <c r="H198" s="64" t="n"/>
@@ -3535,10 +3535,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B199" s="19" t="n"/>
-      <c r="C199" s="65" t="n"/>
-      <c r="D199" s="65" t="n"/>
-      <c r="E199" s="19" t="n"/>
+      <c r="B199" s="64" t="n"/>
+      <c r="C199" s="64" t="n"/>
+      <c r="D199" s="64" t="n"/>
+      <c r="E199" s="64" t="n"/>
       <c r="F199" s="64" t="n"/>
       <c r="G199" s="64" t="n"/>
       <c r="H199" s="64" t="n"/>
@@ -3549,10 +3549,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B200" s="19" t="n"/>
-      <c r="C200" s="65" t="n"/>
-      <c r="D200" s="65" t="n"/>
-      <c r="E200" s="19" t="n"/>
+      <c r="B200" s="64" t="n"/>
+      <c r="C200" s="64" t="n"/>
+      <c r="D200" s="64" t="n"/>
+      <c r="E200" s="64" t="n"/>
       <c r="F200" s="64" t="n"/>
       <c r="G200" s="64" t="n"/>
       <c r="H200" s="64" t="n"/>
@@ -3563,10 +3563,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B201" s="19" t="n"/>
-      <c r="C201" s="65" t="n"/>
-      <c r="D201" s="65" t="n"/>
-      <c r="E201" s="19" t="n"/>
+      <c r="B201" s="64" t="n"/>
+      <c r="C201" s="64" t="n"/>
+      <c r="D201" s="64" t="n"/>
+      <c r="E201" s="64" t="n"/>
       <c r="F201" s="64" t="n"/>
       <c r="G201" s="64" t="n"/>
       <c r="H201" s="64" t="n"/>
@@ -3577,10 +3577,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B202" s="19" t="n"/>
-      <c r="C202" s="65" t="n"/>
-      <c r="D202" s="65" t="n"/>
-      <c r="E202" s="19" t="n"/>
+      <c r="B202" s="64" t="n"/>
+      <c r="C202" s="64" t="n"/>
+      <c r="D202" s="64" t="n"/>
+      <c r="E202" s="64" t="n"/>
       <c r="F202" s="64" t="n"/>
       <c r="G202" s="64" t="n"/>
       <c r="H202" s="64" t="n"/>
@@ -3591,10 +3591,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B203" s="19" t="n"/>
-      <c r="C203" s="65" t="n"/>
-      <c r="D203" s="65" t="n"/>
-      <c r="E203" s="19" t="n"/>
+      <c r="B203" s="64" t="n"/>
+      <c r="C203" s="64" t="n"/>
+      <c r="D203" s="64" t="n"/>
+      <c r="E203" s="64" t="n"/>
       <c r="F203" s="64" t="n"/>
       <c r="G203" s="64" t="n"/>
       <c r="H203" s="64" t="n"/>
@@ -3605,10 +3605,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B204" s="19" t="n"/>
-      <c r="C204" s="65" t="n"/>
-      <c r="D204" s="65" t="n"/>
-      <c r="E204" s="19" t="n"/>
+      <c r="B204" s="64" t="n"/>
+      <c r="C204" s="64" t="n"/>
+      <c r="D204" s="64" t="n"/>
+      <c r="E204" s="64" t="n"/>
       <c r="F204" s="64" t="n"/>
       <c r="G204" s="64" t="n"/>
       <c r="H204" s="64" t="n"/>
@@ -3618,9 +3618,12 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="A5:A204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="현지추천단체구분" error="목록에서 선택하세요. 비워두면 FIMS 값을 그대로 둡니다." promptTitle="현지추천단체구분" prompt="비워두면 FIMS에 입력된 값을 그대로 둡니다. 바꿀 때만 선택하세요." type="list">
+      <formula1>"대학자체현지모집,현지유학원추천,개인직접신청,현지자매학교추천,기타"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3633,19 +3636,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:M204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="62" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3685,30 +3691,45 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
+          <t>현지추천단체구분</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>현지추천단체</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>최종출신학교</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>처리결과</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>확인된 입국일자</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>상세메시지</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>처리일시</t>
         </is>
